--- a/SpaceDebris_site_1000/2013-072P_GEMSat_attached_to_Centaur-5_SEC_upper_s.xlsx
+++ b/SpaceDebris_site_1000/2013-072P_GEMSat_attached_to_Centaur-5_SEC_upper_s.xlsx
@@ -452,7002 +452,7002 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105.66</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="B2" t="n">
-        <v>45468</v>
+        <v>36767</v>
       </c>
       <c r="C2" t="n">
-        <v>104.97</v>
+        <v>6.63</v>
       </c>
       <c r="D2" t="n">
-        <v>28455</v>
+        <v>25261</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110.56</v>
+        <v>0.65</v>
       </c>
       <c r="B3" t="n">
-        <v>32714</v>
+        <v>36560</v>
       </c>
       <c r="C3" t="n">
-        <v>108.6</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>29530</v>
+        <v>27299</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>93.91</v>
+        <v>1.09</v>
       </c>
       <c r="B4" t="n">
-        <v>30929</v>
+        <v>38156</v>
       </c>
       <c r="C4" t="n">
-        <v>90.25</v>
+        <v>4.94</v>
       </c>
       <c r="D4" t="n">
-        <v>11451</v>
+        <v>27606</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96.72</v>
+        <v>1.48</v>
       </c>
       <c r="B5" t="n">
-        <v>37322</v>
+        <v>37364</v>
       </c>
       <c r="C5" t="n">
-        <v>100.61</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>20792</v>
+        <v>10918</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107.01</v>
+        <v>1.54</v>
       </c>
       <c r="B6" t="n">
-        <v>45856</v>
+        <v>34951</v>
       </c>
       <c r="C6" t="n">
-        <v>109.83</v>
+        <v>0.14</v>
       </c>
       <c r="D6" t="n">
-        <v>15041</v>
+        <v>12798</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>149.59</v>
+        <v>1.61</v>
       </c>
       <c r="B7" t="n">
-        <v>23728</v>
+        <v>35783</v>
       </c>
       <c r="C7" t="n">
-        <v>150.54</v>
+        <v>2.25</v>
       </c>
       <c r="D7" t="n">
-        <v>21245</v>
+        <v>20522</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105.74</v>
+        <v>1.87</v>
       </c>
       <c r="B8" t="n">
-        <v>49497</v>
+        <v>37477</v>
       </c>
       <c r="C8" t="n">
-        <v>104.99</v>
+        <v>9.33</v>
       </c>
       <c r="D8" t="n">
-        <v>29654</v>
+        <v>20716</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102.57</v>
+        <v>2.51</v>
       </c>
       <c r="B9" t="n">
-        <v>45978</v>
+        <v>38087</v>
       </c>
       <c r="C9" t="n">
-        <v>103.3</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>24643</v>
+        <v>18429</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113.1</v>
+        <v>3.18</v>
       </c>
       <c r="B10" t="n">
-        <v>24591</v>
+        <v>36984</v>
       </c>
       <c r="C10" t="n">
-        <v>113.54</v>
+        <v>9.98</v>
       </c>
       <c r="D10" t="n">
-        <v>14927</v>
+        <v>25886</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>32.65</v>
+        <v>3.3</v>
       </c>
       <c r="B11" t="n">
-        <v>23500</v>
+        <v>36847</v>
       </c>
       <c r="C11" t="n">
-        <v>32.85</v>
+        <v>3.29</v>
       </c>
       <c r="D11" t="n">
-        <v>13615</v>
+        <v>13288</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95.23</v>
+        <v>3.35</v>
       </c>
       <c r="B12" t="n">
-        <v>34482</v>
+        <v>36769</v>
       </c>
       <c r="C12" t="n">
-        <v>97.37</v>
+        <v>14.69</v>
       </c>
       <c r="D12" t="n">
-        <v>14496</v>
+        <v>15963</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110.55</v>
+        <v>3.37</v>
       </c>
       <c r="B13" t="n">
-        <v>28568</v>
+        <v>36695</v>
       </c>
       <c r="C13" t="n">
-        <v>109.35</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>17217</v>
+        <v>25712</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104.78</v>
+        <v>3.71</v>
       </c>
       <c r="B14" t="n">
-        <v>42924</v>
+        <v>35324</v>
       </c>
       <c r="C14" t="n">
-        <v>107.16</v>
+        <v>1.15</v>
       </c>
       <c r="D14" t="n">
-        <v>28592</v>
+        <v>24845</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>82.11</v>
+        <v>3.81</v>
       </c>
       <c r="B15" t="n">
-        <v>24364</v>
+        <v>36561</v>
       </c>
       <c r="C15" t="n">
-        <v>79.88</v>
+        <v>6.13</v>
       </c>
       <c r="D15" t="n">
-        <v>15544</v>
+        <v>15320</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>37.81</v>
+        <v>4.16</v>
       </c>
       <c r="B16" t="n">
-        <v>21075</v>
+        <v>35507</v>
       </c>
       <c r="C16" t="n">
-        <v>38.13</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>16002</v>
+        <v>28846</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>92.44</v>
+        <v>4.41</v>
       </c>
       <c r="B17" t="n">
-        <v>29451</v>
+        <v>34794</v>
       </c>
       <c r="C17" t="n">
-        <v>95.66</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>27082</v>
+        <v>12196</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>90.28</v>
+        <v>5.14</v>
       </c>
       <c r="B18" t="n">
-        <v>24418</v>
+        <v>34493</v>
       </c>
       <c r="C18" t="n">
-        <v>87.20999999999999</v>
+        <v>4.41</v>
       </c>
       <c r="D18" t="n">
-        <v>19444</v>
+        <v>25264</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>100.88</v>
+        <v>5.46</v>
       </c>
       <c r="B19" t="n">
-        <v>42963</v>
+        <v>35656</v>
       </c>
       <c r="C19" t="n">
-        <v>102.37</v>
+        <v>3.76</v>
       </c>
       <c r="D19" t="n">
-        <v>29789</v>
+        <v>23283</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>109.72</v>
+        <v>6.06</v>
       </c>
       <c r="B20" t="n">
-        <v>32743</v>
+        <v>33140</v>
       </c>
       <c r="C20" t="n">
-        <v>106.69</v>
+        <v>7.21</v>
       </c>
       <c r="D20" t="n">
-        <v>26329</v>
+        <v>19103</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>139.18</v>
+        <v>6.29</v>
       </c>
       <c r="B21" t="n">
-        <v>24437</v>
+        <v>33944</v>
       </c>
       <c r="C21" t="n">
-        <v>136.72</v>
+        <v>4.48</v>
       </c>
       <c r="D21" t="n">
-        <v>17045</v>
+        <v>19304</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>110.87</v>
+        <v>6.74</v>
       </c>
       <c r="B22" t="n">
-        <v>27804</v>
+        <v>34006</v>
       </c>
       <c r="C22" t="n">
-        <v>110.62</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>29168</v>
+        <v>16588</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110.41</v>
+        <v>6.94</v>
       </c>
       <c r="B23" t="n">
-        <v>30888</v>
+        <v>34370</v>
       </c>
       <c r="C23" t="n">
-        <v>113.25</v>
+        <v>1.13</v>
       </c>
       <c r="D23" t="n">
-        <v>15955</v>
+        <v>13272</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>100.98</v>
+        <v>7.02</v>
       </c>
       <c r="B24" t="n">
-        <v>46051</v>
+        <v>34533</v>
       </c>
       <c r="C24" t="n">
-        <v>98.42</v>
+        <v>4.01</v>
       </c>
       <c r="D24" t="n">
-        <v>18386</v>
+        <v>14208</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104.47</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="B25" t="n">
-        <v>47687</v>
+        <v>32375</v>
       </c>
       <c r="C25" t="n">
-        <v>105.52</v>
+        <v>4.83</v>
       </c>
       <c r="D25" t="n">
-        <v>16229</v>
+        <v>19553</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>114.16</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="B26" t="n">
-        <v>23297</v>
+        <v>32614</v>
       </c>
       <c r="C26" t="n">
-        <v>113.33</v>
+        <v>7.46</v>
       </c>
       <c r="D26" t="n">
-        <v>26677</v>
+        <v>27623</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>110.13</v>
+        <v>9.34</v>
       </c>
       <c r="B27" t="n">
-        <v>34512</v>
+        <v>32443</v>
       </c>
       <c r="C27" t="n">
-        <v>107.8</v>
+        <v>12.6</v>
       </c>
       <c r="D27" t="n">
-        <v>20445</v>
+        <v>20373</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>103.44</v>
+        <v>9.35</v>
       </c>
       <c r="B28" t="n">
-        <v>47733</v>
+        <v>30271</v>
       </c>
       <c r="C28" t="n">
-        <v>100.4</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>10269</v>
+        <v>21624</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>92.79000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="B29" t="n">
-        <v>30558</v>
+        <v>29398</v>
       </c>
       <c r="C29" t="n">
-        <v>95.39</v>
+        <v>18.14</v>
       </c>
       <c r="D29" t="n">
-        <v>29649</v>
+        <v>15605</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>90.28</v>
+        <v>11.01</v>
       </c>
       <c r="B30" t="n">
-        <v>26081</v>
+        <v>29835</v>
       </c>
       <c r="C30" t="n">
-        <v>89.17</v>
+        <v>21.89</v>
       </c>
       <c r="D30" t="n">
-        <v>27134</v>
+        <v>13326</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>90.51000000000001</v>
+        <v>11.53</v>
       </c>
       <c r="B31" t="n">
-        <v>26518</v>
+        <v>26394</v>
       </c>
       <c r="C31" t="n">
-        <v>88.59999999999999</v>
+        <v>11.13</v>
       </c>
       <c r="D31" t="n">
-        <v>29473</v>
+        <v>18482</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109.69</v>
+        <v>13.31</v>
       </c>
       <c r="B32" t="n">
-        <v>30770</v>
+        <v>28383</v>
       </c>
       <c r="C32" t="n">
-        <v>109.58</v>
+        <v>3.44</v>
       </c>
       <c r="D32" t="n">
-        <v>18910</v>
+        <v>16355</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>94.56</v>
+        <v>13.78</v>
       </c>
       <c r="B33" t="n">
-        <v>34286</v>
+        <v>30133</v>
       </c>
       <c r="C33" t="n">
-        <v>95.63</v>
+        <v>13.04</v>
       </c>
       <c r="D33" t="n">
-        <v>20367</v>
+        <v>10399</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>93.05</v>
+        <v>14</v>
       </c>
       <c r="B34" t="n">
-        <v>27654</v>
+        <v>26588</v>
       </c>
       <c r="C34" t="n">
-        <v>91.65000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="D34" t="n">
-        <v>19385</v>
+        <v>16773</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>114.65</v>
+        <v>14.95</v>
       </c>
       <c r="B35" t="n">
-        <v>24687</v>
+        <v>28674</v>
       </c>
       <c r="C35" t="n">
-        <v>116.75</v>
+        <v>11.78</v>
       </c>
       <c r="D35" t="n">
-        <v>15464</v>
+        <v>14199</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>102.4</v>
+        <v>15.03</v>
       </c>
       <c r="B36" t="n">
-        <v>47485</v>
+        <v>28589</v>
       </c>
       <c r="C36" t="n">
-        <v>99.59999999999999</v>
+        <v>19.99</v>
       </c>
       <c r="D36" t="n">
-        <v>10615</v>
+        <v>28653</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>97.70999999999999</v>
+        <v>15.27</v>
       </c>
       <c r="B37" t="n">
-        <v>40677</v>
+        <v>25766</v>
       </c>
       <c r="C37" t="n">
-        <v>97.70999999999999</v>
+        <v>7.21</v>
       </c>
       <c r="D37" t="n">
-        <v>22714</v>
+        <v>17343</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>104.65</v>
+        <v>15.32</v>
       </c>
       <c r="B38" t="n">
-        <v>46189</v>
+        <v>25354</v>
       </c>
       <c r="C38" t="n">
-        <v>101.55</v>
+        <v>12.97</v>
       </c>
       <c r="D38" t="n">
-        <v>23207</v>
+        <v>12593</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>110.89</v>
+        <v>15.32</v>
       </c>
       <c r="B39" t="n">
-        <v>29887</v>
+        <v>26617</v>
       </c>
       <c r="C39" t="n">
-        <v>109.2</v>
+        <v>21.87</v>
       </c>
       <c r="D39" t="n">
-        <v>11196</v>
+        <v>15063</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>101.5</v>
+        <v>15.77</v>
       </c>
       <c r="B40" t="n">
-        <v>47662</v>
+        <v>26950</v>
       </c>
       <c r="C40" t="n">
-        <v>102.07</v>
+        <v>12.36</v>
       </c>
       <c r="D40" t="n">
-        <v>10109</v>
+        <v>28042</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>105.16</v>
+        <v>16.37</v>
       </c>
       <c r="B41" t="n">
-        <v>45444</v>
+        <v>25296</v>
       </c>
       <c r="C41" t="n">
-        <v>106.08</v>
+        <v>27.21</v>
       </c>
       <c r="D41" t="n">
-        <v>13399</v>
+        <v>29599</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>97.90000000000001</v>
+        <v>16.38</v>
       </c>
       <c r="B42" t="n">
-        <v>42905</v>
+        <v>25371</v>
       </c>
       <c r="C42" t="n">
-        <v>95.54000000000001</v>
+        <v>22.97</v>
       </c>
       <c r="D42" t="n">
-        <v>16335</v>
+        <v>18888</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>100.09</v>
+        <v>16.93</v>
       </c>
       <c r="B43" t="n">
-        <v>45584</v>
+        <v>26349</v>
       </c>
       <c r="C43" t="n">
-        <v>103.2</v>
+        <v>11.6</v>
       </c>
       <c r="D43" t="n">
-        <v>11220</v>
+        <v>12287</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113.17</v>
+        <v>16.97</v>
       </c>
       <c r="B44" t="n">
-        <v>26019</v>
+        <v>24471</v>
       </c>
       <c r="C44" t="n">
-        <v>113.68</v>
+        <v>18.52</v>
       </c>
       <c r="D44" t="n">
-        <v>25442</v>
+        <v>12992</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>110.23</v>
+        <v>16.98</v>
       </c>
       <c r="B45" t="n">
-        <v>30289</v>
+        <v>26226</v>
       </c>
       <c r="C45" t="n">
-        <v>110.41</v>
+        <v>22.3</v>
       </c>
       <c r="D45" t="n">
-        <v>23291</v>
+        <v>11784</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>108.79</v>
+        <v>17.1</v>
       </c>
       <c r="B46" t="n">
-        <v>36210</v>
+        <v>21736</v>
       </c>
       <c r="C46" t="n">
-        <v>110.77</v>
+        <v>17.67</v>
       </c>
       <c r="D46" t="n">
-        <v>12656</v>
+        <v>11035</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>98.2</v>
+        <v>18.66</v>
       </c>
       <c r="B47" t="n">
-        <v>40924</v>
+        <v>26068</v>
       </c>
       <c r="C47" t="n">
-        <v>100.79</v>
+        <v>19.92</v>
       </c>
       <c r="D47" t="n">
-        <v>27939</v>
+        <v>29257</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>97.3</v>
+        <v>19.47</v>
       </c>
       <c r="B48" t="n">
-        <v>40168</v>
+        <v>24678</v>
       </c>
       <c r="C48" t="n">
-        <v>95.66</v>
+        <v>24.25</v>
       </c>
       <c r="D48" t="n">
-        <v>13401</v>
+        <v>29385</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>103.4</v>
+        <v>19.92</v>
       </c>
       <c r="B49" t="n">
-        <v>46057</v>
+        <v>20598</v>
       </c>
       <c r="C49" t="n">
-        <v>104.06</v>
+        <v>13.76</v>
       </c>
       <c r="D49" t="n">
-        <v>23243</v>
+        <v>28416</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>106.33</v>
+        <v>19.92</v>
       </c>
       <c r="B50" t="n">
-        <v>43693</v>
+        <v>23215</v>
       </c>
       <c r="C50" t="n">
-        <v>106.7</v>
+        <v>25.55</v>
       </c>
       <c r="D50" t="n">
-        <v>18478</v>
+        <v>18746</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>96.73999999999999</v>
+        <v>20.01</v>
       </c>
       <c r="B51" t="n">
-        <v>39361</v>
+        <v>23642</v>
       </c>
       <c r="C51" t="n">
-        <v>99.2</v>
+        <v>17.11</v>
       </c>
       <c r="D51" t="n">
-        <v>13711</v>
+        <v>29954</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>178.82</v>
+        <v>21.11</v>
       </c>
       <c r="B52" t="n">
-        <v>22405</v>
+        <v>24861</v>
       </c>
       <c r="C52" t="n">
-        <v>176.85</v>
+        <v>24.72</v>
       </c>
       <c r="D52" t="n">
-        <v>24840</v>
+        <v>13523</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>97.34</v>
+        <v>21.72</v>
       </c>
       <c r="B53" t="n">
-        <v>38711</v>
+        <v>22216</v>
       </c>
       <c r="C53" t="n">
-        <v>93.09999999999999</v>
+        <v>25.94</v>
       </c>
       <c r="D53" t="n">
-        <v>18182</v>
+        <v>29313</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>98.33</v>
+        <v>21.97</v>
       </c>
       <c r="B54" t="n">
-        <v>41826</v>
+        <v>25240</v>
       </c>
       <c r="C54" t="n">
-        <v>97.38</v>
+        <v>28.78</v>
       </c>
       <c r="D54" t="n">
-        <v>12724</v>
+        <v>11584</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>75.92</v>
+        <v>23.42</v>
       </c>
       <c r="B55" t="n">
-        <v>22255</v>
+        <v>24524</v>
       </c>
       <c r="C55" t="n">
-        <v>75.59999999999999</v>
+        <v>29.35</v>
       </c>
       <c r="D55" t="n">
-        <v>25446</v>
+        <v>15696</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>17.16</v>
+        <v>24.17</v>
       </c>
       <c r="B56" t="n">
-        <v>22853</v>
+        <v>22344</v>
       </c>
       <c r="C56" t="n">
-        <v>17.2</v>
+        <v>20.66</v>
       </c>
       <c r="D56" t="n">
-        <v>28292</v>
+        <v>23928</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>97.89</v>
+        <v>24.43</v>
       </c>
       <c r="B57" t="n">
-        <v>39664</v>
+        <v>20351</v>
       </c>
       <c r="C57" t="n">
-        <v>101.48</v>
+        <v>23.26</v>
       </c>
       <c r="D57" t="n">
-        <v>27286</v>
+        <v>26210</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>166.59</v>
+        <v>25.85</v>
       </c>
       <c r="B58" t="n">
-        <v>23417</v>
+        <v>20966</v>
       </c>
       <c r="C58" t="n">
-        <v>160.67</v>
+        <v>23.43</v>
       </c>
       <c r="D58" t="n">
-        <v>20121</v>
+        <v>26693</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>21.1</v>
+        <v>25.92</v>
       </c>
       <c r="B59" t="n">
-        <v>22524</v>
+        <v>20632</v>
       </c>
       <c r="C59" t="n">
-        <v>20.67</v>
+        <v>26.94</v>
       </c>
       <c r="D59" t="n">
-        <v>19948</v>
+        <v>12287</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>109.35</v>
+        <v>26.14</v>
       </c>
       <c r="B60" t="n">
-        <v>34193</v>
+        <v>19583</v>
       </c>
       <c r="C60" t="n">
-        <v>109.65</v>
+        <v>35.35</v>
       </c>
       <c r="D60" t="n">
-        <v>10653</v>
+        <v>12879</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>29.77</v>
+        <v>26.24</v>
       </c>
       <c r="B61" t="n">
-        <v>26549</v>
+        <v>23085</v>
       </c>
       <c r="C61" t="n">
-        <v>29.97</v>
+        <v>28.63</v>
       </c>
       <c r="D61" t="n">
-        <v>27545</v>
+        <v>17362</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>113.2</v>
+        <v>26.26</v>
       </c>
       <c r="B62" t="n">
-        <v>23375</v>
+        <v>22172</v>
       </c>
       <c r="C62" t="n">
-        <v>116.96</v>
+        <v>36.09</v>
       </c>
       <c r="D62" t="n">
-        <v>24688</v>
+        <v>23672</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>8.550000000000001</v>
+        <v>26.72</v>
       </c>
       <c r="B63" t="n">
-        <v>22490</v>
+        <v>18361</v>
       </c>
       <c r="C63" t="n">
-        <v>8.58</v>
+        <v>18.41</v>
       </c>
       <c r="D63" t="n">
-        <v>18042</v>
+        <v>20383</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>67.02</v>
+        <v>27.45</v>
       </c>
       <c r="B64" t="n">
-        <v>22082</v>
+        <v>20775</v>
       </c>
       <c r="C64" t="n">
-        <v>66.8</v>
+        <v>20.35</v>
       </c>
       <c r="D64" t="n">
-        <v>11469</v>
+        <v>12275</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>105.23</v>
+        <v>27.57</v>
       </c>
       <c r="B65" t="n">
-        <v>45056</v>
+        <v>19626</v>
       </c>
       <c r="C65" t="n">
-        <v>105.91</v>
+        <v>27.51</v>
       </c>
       <c r="D65" t="n">
-        <v>26072</v>
+        <v>17182</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>92.53</v>
+        <v>28</v>
       </c>
       <c r="B66" t="n">
-        <v>24674</v>
+        <v>21277</v>
       </c>
       <c r="C66" t="n">
-        <v>94.89</v>
+        <v>36.15</v>
       </c>
       <c r="D66" t="n">
-        <v>11240</v>
+        <v>15409</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>97.63</v>
+        <v>28.09</v>
       </c>
       <c r="B67" t="n">
-        <v>39710</v>
+        <v>19077</v>
       </c>
       <c r="C67" t="n">
-        <v>94.59</v>
+        <v>23.49</v>
       </c>
       <c r="D67" t="n">
-        <v>22668</v>
+        <v>27714</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>110.35</v>
+        <v>28.54</v>
       </c>
       <c r="B68" t="n">
-        <v>31041</v>
+        <v>19318</v>
       </c>
       <c r="C68" t="n">
-        <v>110.32</v>
+        <v>32.49</v>
       </c>
       <c r="D68" t="n">
-        <v>19224</v>
+        <v>10902</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>112.49</v>
+        <v>28.74</v>
       </c>
       <c r="B69" t="n">
-        <v>26809</v>
+        <v>19876</v>
       </c>
       <c r="C69" t="n">
-        <v>113.23</v>
+        <v>35.05</v>
       </c>
       <c r="D69" t="n">
-        <v>28559</v>
+        <v>16291</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>142.13</v>
+        <v>28.96</v>
       </c>
       <c r="B70" t="n">
-        <v>24014</v>
+        <v>21978</v>
       </c>
       <c r="C70" t="n">
-        <v>139.46</v>
+        <v>26.02</v>
       </c>
       <c r="D70" t="n">
-        <v>25476</v>
+        <v>24459</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>108.76</v>
+        <v>28.98</v>
       </c>
       <c r="B71" t="n">
-        <v>39126</v>
+        <v>24188</v>
       </c>
       <c r="C71" t="n">
-        <v>111.62</v>
+        <v>31.91</v>
       </c>
       <c r="D71" t="n">
-        <v>27423</v>
+        <v>28700</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>105.95</v>
+        <v>29.78</v>
       </c>
       <c r="B72" t="n">
-        <v>44393</v>
+        <v>21176</v>
       </c>
       <c r="C72" t="n">
-        <v>108.83</v>
+        <v>33.8</v>
       </c>
       <c r="D72" t="n">
-        <v>10716</v>
+        <v>29850</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>114.87</v>
+        <v>30.22</v>
       </c>
       <c r="B73" t="n">
-        <v>22696</v>
+        <v>22307</v>
       </c>
       <c r="C73" t="n">
-        <v>119.38</v>
+        <v>22.42</v>
       </c>
       <c r="D73" t="n">
-        <v>27073</v>
+        <v>23101</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>94.12</v>
+        <v>30.34</v>
       </c>
       <c r="B74" t="n">
-        <v>31387</v>
+        <v>21757</v>
       </c>
       <c r="C74" t="n">
-        <v>90.61</v>
+        <v>30.87</v>
       </c>
       <c r="D74" t="n">
-        <v>22361</v>
+        <v>12183</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>102.62</v>
+        <v>31.08</v>
       </c>
       <c r="B75" t="n">
-        <v>46662</v>
+        <v>19120</v>
       </c>
       <c r="C75" t="n">
-        <v>105.13</v>
+        <v>29.31</v>
       </c>
       <c r="D75" t="n">
-        <v>11740</v>
+        <v>25494</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>104.83</v>
+        <v>31.29</v>
       </c>
       <c r="B76" t="n">
-        <v>46000</v>
+        <v>21202</v>
       </c>
       <c r="C76" t="n">
-        <v>102.59</v>
+        <v>26.09</v>
       </c>
       <c r="D76" t="n">
-        <v>18701</v>
+        <v>13705</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>110.53</v>
+        <v>31.53</v>
       </c>
       <c r="B77" t="n">
-        <v>31379</v>
+        <v>20773</v>
       </c>
       <c r="C77" t="n">
-        <v>109.53</v>
+        <v>33.35</v>
       </c>
       <c r="D77" t="n">
-        <v>16993</v>
+        <v>18057</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>95.37</v>
+        <v>32.16</v>
       </c>
       <c r="B78" t="n">
-        <v>35329</v>
+        <v>22762</v>
       </c>
       <c r="C78" t="n">
-        <v>92.06999999999999</v>
+        <v>33.7</v>
       </c>
       <c r="D78" t="n">
-        <v>17349</v>
+        <v>27366</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>95.63</v>
+        <v>33.03</v>
       </c>
       <c r="B79" t="n">
-        <v>35644</v>
+        <v>19830</v>
       </c>
       <c r="C79" t="n">
-        <v>92.77</v>
+        <v>32.48</v>
       </c>
       <c r="D79" t="n">
-        <v>12922</v>
+        <v>23190</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>100.86</v>
+        <v>33.71</v>
       </c>
       <c r="B80" t="n">
-        <v>45497</v>
+        <v>17013</v>
       </c>
       <c r="C80" t="n">
-        <v>99.44</v>
+        <v>38.85</v>
       </c>
       <c r="D80" t="n">
-        <v>17202</v>
+        <v>16953</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>99.44</v>
+        <v>34.3</v>
       </c>
       <c r="B81" t="n">
-        <v>42020</v>
+        <v>20896</v>
       </c>
       <c r="C81" t="n">
-        <v>103.39</v>
+        <v>25.65</v>
       </c>
       <c r="D81" t="n">
-        <v>12975</v>
+        <v>21516</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>10.31</v>
+        <v>34.5</v>
       </c>
       <c r="B82" t="n">
-        <v>23660</v>
+        <v>20548</v>
       </c>
       <c r="C82" t="n">
-        <v>11.09</v>
+        <v>40.09</v>
       </c>
       <c r="D82" t="n">
-        <v>29900</v>
+        <v>14567</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>107.76</v>
+        <v>35.27</v>
       </c>
       <c r="B83" t="n">
-        <v>41593</v>
+        <v>22855</v>
       </c>
       <c r="C83" t="n">
-        <v>106.5</v>
+        <v>30.62</v>
       </c>
       <c r="D83" t="n">
-        <v>23554</v>
+        <v>15748</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>102.54</v>
+        <v>35.38</v>
       </c>
       <c r="B84" t="n">
-        <v>45852</v>
+        <v>19342</v>
       </c>
       <c r="C84" t="n">
-        <v>103.94</v>
+        <v>40.63</v>
       </c>
       <c r="D84" t="n">
-        <v>13612</v>
+        <v>24476</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>101.23</v>
+        <v>35.83</v>
       </c>
       <c r="B85" t="n">
-        <v>45992</v>
+        <v>21976</v>
       </c>
       <c r="C85" t="n">
-        <v>100.11</v>
+        <v>37.46</v>
       </c>
       <c r="D85" t="n">
-        <v>13688</v>
+        <v>15714</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>93.13</v>
+        <v>36.08</v>
       </c>
       <c r="B86" t="n">
-        <v>26693</v>
+        <v>21431</v>
       </c>
       <c r="C86" t="n">
-        <v>89.44</v>
+        <v>33.06</v>
       </c>
       <c r="D86" t="n">
-        <v>28598</v>
+        <v>12330</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>109.07</v>
+        <v>36.14</v>
       </c>
       <c r="B87" t="n">
-        <v>33116</v>
+        <v>21144</v>
       </c>
       <c r="C87" t="n">
-        <v>106.87</v>
+        <v>32.3</v>
       </c>
       <c r="D87" t="n">
-        <v>25731</v>
+        <v>16705</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>110.33</v>
+        <v>36.17</v>
       </c>
       <c r="B88" t="n">
-        <v>31234</v>
+        <v>20740</v>
       </c>
       <c r="C88" t="n">
-        <v>110.12</v>
+        <v>31.33</v>
       </c>
       <c r="D88" t="n">
-        <v>11904</v>
+        <v>14864</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>101.93</v>
+        <v>36.35</v>
       </c>
       <c r="B89" t="n">
-        <v>45721</v>
+        <v>21344</v>
       </c>
       <c r="C89" t="n">
-        <v>103.54</v>
+        <v>37.66</v>
       </c>
       <c r="D89" t="n">
-        <v>18238</v>
+        <v>25860</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>106.28</v>
+        <v>36.66</v>
       </c>
       <c r="B90" t="n">
-        <v>41254</v>
+        <v>21000</v>
       </c>
       <c r="C90" t="n">
-        <v>101.38</v>
+        <v>36.78</v>
       </c>
       <c r="D90" t="n">
-        <v>14213</v>
+        <v>10805</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>102.6</v>
+        <v>37.08</v>
       </c>
       <c r="B91" t="n">
-        <v>47892</v>
+        <v>23367</v>
       </c>
       <c r="C91" t="n">
-        <v>106.7</v>
+        <v>42.69</v>
       </c>
       <c r="D91" t="n">
-        <v>23969</v>
+        <v>26005</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>93.3</v>
+        <v>37.28</v>
       </c>
       <c r="B92" t="n">
-        <v>24414</v>
+        <v>22232</v>
       </c>
       <c r="C92" t="n">
-        <v>93.62</v>
+        <v>39.92</v>
       </c>
       <c r="D92" t="n">
-        <v>18310</v>
+        <v>16258</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>178.39</v>
+        <v>37.3</v>
       </c>
       <c r="B93" t="n">
-        <v>23329</v>
+        <v>19633</v>
       </c>
       <c r="C93" t="n">
-        <v>174.91</v>
+        <v>34.6</v>
       </c>
       <c r="D93" t="n">
-        <v>11629</v>
+        <v>11039</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>174.51</v>
+        <v>37.5</v>
       </c>
       <c r="B94" t="n">
-        <v>21565</v>
+        <v>20975</v>
       </c>
       <c r="C94" t="n">
-        <v>178.02</v>
+        <v>42.74</v>
       </c>
       <c r="D94" t="n">
-        <v>26010</v>
+        <v>28783</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>105.51</v>
+        <v>37.6</v>
       </c>
       <c r="B95" t="n">
-        <v>46410</v>
+        <v>20545</v>
       </c>
       <c r="C95" t="n">
-        <v>101.97</v>
+        <v>26.86</v>
       </c>
       <c r="D95" t="n">
-        <v>19250</v>
+        <v>21171</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>13.13</v>
+        <v>37.87</v>
       </c>
       <c r="B96" t="n">
-        <v>21905</v>
+        <v>24826</v>
       </c>
       <c r="C96" t="n">
-        <v>12.93</v>
+        <v>40.28</v>
       </c>
       <c r="D96" t="n">
-        <v>10640</v>
+        <v>27544</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>98.98999999999999</v>
+        <v>38.61</v>
       </c>
       <c r="B97" t="n">
-        <v>42531</v>
+        <v>22292</v>
       </c>
       <c r="C97" t="n">
-        <v>97.38</v>
+        <v>25.61</v>
       </c>
       <c r="D97" t="n">
-        <v>27552</v>
+        <v>28729</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>103.62</v>
+        <v>38.68</v>
       </c>
       <c r="B98" t="n">
-        <v>47936</v>
+        <v>23823</v>
       </c>
       <c r="C98" t="n">
-        <v>102.19</v>
+        <v>37.66</v>
       </c>
       <c r="D98" t="n">
-        <v>24659</v>
+        <v>12197</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>147.99</v>
+        <v>38.85</v>
       </c>
       <c r="B99" t="n">
-        <v>23276</v>
+        <v>21444</v>
       </c>
       <c r="C99" t="n">
-        <v>144.12</v>
+        <v>29.67</v>
       </c>
       <c r="D99" t="n">
-        <v>20933</v>
+        <v>13650</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>114.07</v>
+        <v>39.51</v>
       </c>
       <c r="B100" t="n">
-        <v>24232</v>
+        <v>20859</v>
       </c>
       <c r="C100" t="n">
-        <v>113.77</v>
+        <v>46.14</v>
       </c>
       <c r="D100" t="n">
-        <v>29242</v>
+        <v>25102</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>110.8</v>
+        <v>40.17</v>
       </c>
       <c r="B101" t="n">
-        <v>29882</v>
+        <v>22789</v>
       </c>
       <c r="C101" t="n">
-        <v>115.26</v>
+        <v>44.41</v>
       </c>
       <c r="D101" t="n">
-        <v>17949</v>
+        <v>25452</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>92.27</v>
+        <v>40.24</v>
       </c>
       <c r="B102" t="n">
-        <v>29992</v>
+        <v>23866</v>
       </c>
       <c r="C102" t="n">
-        <v>90.48</v>
+        <v>39.6</v>
       </c>
       <c r="D102" t="n">
-        <v>12987</v>
+        <v>19821</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>161.44</v>
+        <v>40.41</v>
       </c>
       <c r="B103" t="n">
-        <v>22583</v>
+        <v>22182</v>
       </c>
       <c r="C103" t="n">
-        <v>156.88</v>
+        <v>34.67</v>
       </c>
       <c r="D103" t="n">
-        <v>10201</v>
+        <v>28206</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>103.05</v>
+        <v>40.76</v>
       </c>
       <c r="B104" t="n">
-        <v>45434</v>
+        <v>20340</v>
       </c>
       <c r="C104" t="n">
-        <v>105.39</v>
+        <v>40.48</v>
       </c>
       <c r="D104" t="n">
-        <v>26445</v>
+        <v>10384</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>96.53</v>
+        <v>40.78</v>
       </c>
       <c r="B105" t="n">
-        <v>36755</v>
+        <v>20362</v>
       </c>
       <c r="C105" t="n">
-        <v>96.97</v>
+        <v>36.67</v>
       </c>
       <c r="D105" t="n">
-        <v>24734</v>
+        <v>25957</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>113.87</v>
+        <v>41.05</v>
       </c>
       <c r="B106" t="n">
-        <v>25443</v>
+        <v>22625</v>
       </c>
       <c r="C106" t="n">
-        <v>117.71</v>
+        <v>40.59</v>
       </c>
       <c r="D106" t="n">
-        <v>28395</v>
+        <v>12052</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>102.32</v>
+        <v>42.12</v>
       </c>
       <c r="B107" t="n">
-        <v>46829</v>
+        <v>21828</v>
       </c>
       <c r="C107" t="n">
-        <v>103.55</v>
+        <v>36.14</v>
       </c>
       <c r="D107" t="n">
-        <v>23753</v>
+        <v>13997</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>177.08</v>
+        <v>42.12</v>
       </c>
       <c r="B108" t="n">
-        <v>24023</v>
+        <v>19350</v>
       </c>
       <c r="C108" t="n">
-        <v>177.17</v>
+        <v>40.82</v>
       </c>
       <c r="D108" t="n">
-        <v>20727</v>
+        <v>26263</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>95.37</v>
+        <v>42.28</v>
       </c>
       <c r="B109" t="n">
-        <v>34528</v>
+        <v>22282</v>
       </c>
       <c r="C109" t="n">
-        <v>95.93000000000001</v>
+        <v>46.17</v>
       </c>
       <c r="D109" t="n">
-        <v>29990</v>
+        <v>15277</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>136.44</v>
+        <v>42.91</v>
       </c>
       <c r="B110" t="n">
-        <v>26017</v>
+        <v>20650</v>
       </c>
       <c r="C110" t="n">
-        <v>135.16</v>
+        <v>57.49</v>
       </c>
       <c r="D110" t="n">
-        <v>24833</v>
+        <v>15398</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>112.62</v>
+        <v>43.22</v>
       </c>
       <c r="B111" t="n">
-        <v>25365</v>
+        <v>21393</v>
       </c>
       <c r="C111" t="n">
-        <v>110.94</v>
+        <v>34.33</v>
       </c>
       <c r="D111" t="n">
-        <v>15766</v>
+        <v>23364</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>91.79000000000001</v>
+        <v>43.35</v>
       </c>
       <c r="B112" t="n">
-        <v>24782</v>
+        <v>19360</v>
       </c>
       <c r="C112" t="n">
-        <v>94.76000000000001</v>
+        <v>47.55</v>
       </c>
       <c r="D112" t="n">
-        <v>16102</v>
+        <v>11145</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>106.02</v>
+        <v>43.39</v>
       </c>
       <c r="B113" t="n">
-        <v>42204</v>
+        <v>22242</v>
       </c>
       <c r="C113" t="n">
-        <v>103.53</v>
+        <v>42.98</v>
       </c>
       <c r="D113" t="n">
-        <v>18574</v>
+        <v>24480</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>111.24</v>
+        <v>43.49</v>
       </c>
       <c r="B114" t="n">
-        <v>28214</v>
+        <v>20716</v>
       </c>
       <c r="C114" t="n">
-        <v>112.22</v>
+        <v>35.86</v>
       </c>
       <c r="D114" t="n">
-        <v>10645</v>
+        <v>13542</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>102.67</v>
+        <v>43.69</v>
       </c>
       <c r="B115" t="n">
-        <v>48920</v>
+        <v>22807</v>
       </c>
       <c r="C115" t="n">
-        <v>102.78</v>
+        <v>51.66</v>
       </c>
       <c r="D115" t="n">
-        <v>19250</v>
+        <v>20444</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>90.75</v>
+        <v>43.78</v>
       </c>
       <c r="B116" t="n">
-        <v>23184</v>
+        <v>21503</v>
       </c>
       <c r="C116" t="n">
-        <v>89.61</v>
+        <v>35.77</v>
       </c>
       <c r="D116" t="n">
-        <v>27965</v>
+        <v>11054</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>91.81999999999999</v>
+        <v>43.96</v>
       </c>
       <c r="B117" t="n">
-        <v>25552</v>
+        <v>24450</v>
       </c>
       <c r="C117" t="n">
-        <v>89.09</v>
+        <v>44.4</v>
       </c>
       <c r="D117" t="n">
-        <v>22446</v>
+        <v>25811</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>107.02</v>
+        <v>44.3</v>
       </c>
       <c r="B118" t="n">
-        <v>42017</v>
+        <v>21970</v>
       </c>
       <c r="C118" t="n">
-        <v>105.64</v>
+        <v>49.36</v>
       </c>
       <c r="D118" t="n">
-        <v>15332</v>
+        <v>28593</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>101.34</v>
+        <v>45.12</v>
       </c>
       <c r="B119" t="n">
-        <v>48674</v>
+        <v>20555</v>
       </c>
       <c r="C119" t="n">
-        <v>105.52</v>
+        <v>46.07</v>
       </c>
       <c r="D119" t="n">
-        <v>12792</v>
+        <v>29499</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>98.16</v>
+        <v>45.65</v>
       </c>
       <c r="B120" t="n">
-        <v>41331</v>
+        <v>20513</v>
       </c>
       <c r="C120" t="n">
-        <v>100.33</v>
+        <v>42.95</v>
       </c>
       <c r="D120" t="n">
-        <v>20623</v>
+        <v>11510</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>99.43000000000001</v>
+        <v>46.81</v>
       </c>
       <c r="B121" t="n">
-        <v>44387</v>
+        <v>23162</v>
       </c>
       <c r="C121" t="n">
-        <v>103.32</v>
+        <v>58.75</v>
       </c>
       <c r="D121" t="n">
-        <v>18127</v>
+        <v>23925</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>38.73</v>
+        <v>47.07</v>
       </c>
       <c r="B122" t="n">
-        <v>22188</v>
+        <v>22388</v>
       </c>
       <c r="C122" t="n">
-        <v>40.48</v>
+        <v>39.6</v>
       </c>
       <c r="D122" t="n">
-        <v>17804</v>
+        <v>14383</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>104.49</v>
+        <v>47.58</v>
       </c>
       <c r="B123" t="n">
-        <v>45768</v>
+        <v>21565</v>
       </c>
       <c r="C123" t="n">
-        <v>100.61</v>
+        <v>58.59</v>
       </c>
       <c r="D123" t="n">
-        <v>24356</v>
+        <v>13010</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>92.05</v>
+        <v>47.64</v>
       </c>
       <c r="B124" t="n">
-        <v>25784</v>
+        <v>21441</v>
       </c>
       <c r="C124" t="n">
-        <v>92.27</v>
+        <v>44.26</v>
       </c>
       <c r="D124" t="n">
-        <v>13806</v>
+        <v>18147</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>94.75</v>
+        <v>47.84</v>
       </c>
       <c r="B125" t="n">
-        <v>34957</v>
+        <v>22354</v>
       </c>
       <c r="C125" t="n">
-        <v>93.34</v>
+        <v>47.71</v>
       </c>
       <c r="D125" t="n">
-        <v>28837</v>
+        <v>26037</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>108.17</v>
+        <v>48.22</v>
       </c>
       <c r="B126" t="n">
-        <v>39042</v>
+        <v>20051</v>
       </c>
       <c r="C126" t="n">
-        <v>107.13</v>
+        <v>53.96</v>
       </c>
       <c r="D126" t="n">
-        <v>24561</v>
+        <v>27732</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>112.98</v>
+        <v>48.54</v>
       </c>
       <c r="B127" t="n">
-        <v>24302</v>
+        <v>22400</v>
       </c>
       <c r="C127" t="n">
-        <v>109.02</v>
+        <v>40.07</v>
       </c>
       <c r="D127" t="n">
-        <v>12154</v>
+        <v>15178</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>107.62</v>
+        <v>48.69</v>
       </c>
       <c r="B128" t="n">
-        <v>38864</v>
+        <v>22499</v>
       </c>
       <c r="C128" t="n">
-        <v>111.82</v>
+        <v>48.26</v>
       </c>
       <c r="D128" t="n">
-        <v>12138</v>
+        <v>24717</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>90.93000000000001</v>
+        <v>48.76</v>
       </c>
       <c r="B129" t="n">
-        <v>26048</v>
+        <v>21752</v>
       </c>
       <c r="C129" t="n">
-        <v>92.11</v>
+        <v>40.72</v>
       </c>
       <c r="D129" t="n">
-        <v>11606</v>
+        <v>20123</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>110.89</v>
+        <v>49.42</v>
       </c>
       <c r="B130" t="n">
-        <v>29218</v>
+        <v>19846</v>
       </c>
       <c r="C130" t="n">
-        <v>111.36</v>
+        <v>38.5</v>
       </c>
       <c r="D130" t="n">
-        <v>16503</v>
+        <v>17880</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>95.38</v>
+        <v>49.6</v>
       </c>
       <c r="B131" t="n">
-        <v>35750</v>
+        <v>20616</v>
       </c>
       <c r="C131" t="n">
-        <v>98.20999999999999</v>
+        <v>48.11</v>
       </c>
       <c r="D131" t="n">
-        <v>21035</v>
+        <v>11028</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>102.75</v>
+        <v>50.13</v>
       </c>
       <c r="B132" t="n">
-        <v>48576</v>
+        <v>17802</v>
       </c>
       <c r="C132" t="n">
-        <v>105.94</v>
+        <v>49.79</v>
       </c>
       <c r="D132" t="n">
-        <v>21572</v>
+        <v>11993</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>39.78</v>
+        <v>50.18</v>
       </c>
       <c r="B133" t="n">
-        <v>22362</v>
+        <v>21017</v>
       </c>
       <c r="C133" t="n">
-        <v>39.81</v>
+        <v>57.91</v>
       </c>
       <c r="D133" t="n">
-        <v>27979</v>
+        <v>25082</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>97.73999999999999</v>
+        <v>51.29</v>
       </c>
       <c r="B134" t="n">
-        <v>39566</v>
+        <v>20320</v>
       </c>
       <c r="C134" t="n">
-        <v>101.02</v>
+        <v>33.99</v>
       </c>
       <c r="D134" t="n">
-        <v>25699</v>
+        <v>12953</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>103.51</v>
+        <v>51.34</v>
       </c>
       <c r="B135" t="n">
-        <v>47598</v>
+        <v>22934</v>
       </c>
       <c r="C135" t="n">
-        <v>103.1</v>
+        <v>53.79</v>
       </c>
       <c r="D135" t="n">
-        <v>14670</v>
+        <v>24702</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>96.5</v>
+        <v>51.83</v>
       </c>
       <c r="B136" t="n">
-        <v>38875</v>
+        <v>19571</v>
       </c>
       <c r="C136" t="n">
-        <v>97.13</v>
+        <v>47.76</v>
       </c>
       <c r="D136" t="n">
-        <v>19593</v>
+        <v>28941</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>111.4</v>
+        <v>52.3</v>
       </c>
       <c r="B137" t="n">
-        <v>29055</v>
+        <v>20158</v>
       </c>
       <c r="C137" t="n">
-        <v>108.59</v>
+        <v>63.94</v>
       </c>
       <c r="D137" t="n">
-        <v>23402</v>
+        <v>24780</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>111.72</v>
+        <v>53.05</v>
       </c>
       <c r="B138" t="n">
-        <v>25906</v>
+        <v>20918</v>
       </c>
       <c r="C138" t="n">
-        <v>113.21</v>
+        <v>46.33</v>
       </c>
       <c r="D138" t="n">
-        <v>25238</v>
+        <v>23857</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>94.12</v>
+        <v>53.22</v>
       </c>
       <c r="B139" t="n">
-        <v>30382</v>
+        <v>19498</v>
       </c>
       <c r="C139" t="n">
-        <v>92.92</v>
+        <v>48.92</v>
       </c>
       <c r="D139" t="n">
-        <v>10792</v>
+        <v>11864</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>81.15000000000001</v>
+        <v>53.56</v>
       </c>
       <c r="B140" t="n">
-        <v>27378</v>
+        <v>18787</v>
       </c>
       <c r="C140" t="n">
-        <v>82.67</v>
+        <v>59.55</v>
       </c>
       <c r="D140" t="n">
-        <v>26927</v>
+        <v>17200</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>98.3</v>
+        <v>53.75</v>
       </c>
       <c r="B141" t="n">
-        <v>41236</v>
+        <v>21650</v>
       </c>
       <c r="C141" t="n">
-        <v>99.45</v>
+        <v>47.56</v>
       </c>
       <c r="D141" t="n">
-        <v>13656</v>
+        <v>16487</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>95</v>
+        <v>53.9</v>
       </c>
       <c r="B142" t="n">
-        <v>31422</v>
+        <v>20324</v>
       </c>
       <c r="C142" t="n">
-        <v>94.83</v>
+        <v>44.08</v>
       </c>
       <c r="D142" t="n">
-        <v>21397</v>
+        <v>11647</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>63.83</v>
+        <v>54.34</v>
       </c>
       <c r="B143" t="n">
-        <v>23981</v>
+        <v>18738</v>
       </c>
       <c r="C143" t="n">
-        <v>61.95</v>
+        <v>55.05</v>
       </c>
       <c r="D143" t="n">
-        <v>21814</v>
+        <v>27486</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>112.57</v>
+        <v>54.96</v>
       </c>
       <c r="B144" t="n">
-        <v>25021</v>
+        <v>23124</v>
       </c>
       <c r="C144" t="n">
-        <v>110.7</v>
+        <v>59.25</v>
       </c>
       <c r="D144" t="n">
-        <v>20594</v>
+        <v>12923</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>100.93</v>
+        <v>54.96</v>
       </c>
       <c r="B145" t="n">
-        <v>46251</v>
+        <v>22588</v>
       </c>
       <c r="C145" t="n">
-        <v>98.09</v>
+        <v>41.05</v>
       </c>
       <c r="D145" t="n">
-        <v>26221</v>
+        <v>16981</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>102.84</v>
+        <v>54.97</v>
       </c>
       <c r="B146" t="n">
-        <v>47332</v>
+        <v>21496</v>
       </c>
       <c r="C146" t="n">
-        <v>101.24</v>
+        <v>51.63</v>
       </c>
       <c r="D146" t="n">
-        <v>14563</v>
+        <v>23497</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>34.6</v>
+        <v>55.41</v>
       </c>
       <c r="B147" t="n">
-        <v>23892</v>
+        <v>20628</v>
       </c>
       <c r="C147" t="n">
-        <v>33.87</v>
+        <v>59.94</v>
       </c>
       <c r="D147" t="n">
-        <v>14390</v>
+        <v>16992</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>93.31999999999999</v>
+        <v>55.56</v>
       </c>
       <c r="B148" t="n">
-        <v>27108</v>
+        <v>20891</v>
       </c>
       <c r="C148" t="n">
-        <v>97.03</v>
+        <v>56.07</v>
       </c>
       <c r="D148" t="n">
-        <v>24735</v>
+        <v>25287</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>147.68</v>
+        <v>55.78</v>
       </c>
       <c r="B149" t="n">
-        <v>23824</v>
+        <v>20390</v>
       </c>
       <c r="C149" t="n">
-        <v>148.66</v>
+        <v>53.73</v>
       </c>
       <c r="D149" t="n">
-        <v>27192</v>
+        <v>24864</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>94.88</v>
+        <v>55.91</v>
       </c>
       <c r="B150" t="n">
-        <v>34903</v>
+        <v>21533</v>
       </c>
       <c r="C150" t="n">
-        <v>95.52</v>
+        <v>50.03</v>
       </c>
       <c r="D150" t="n">
-        <v>22379</v>
+        <v>20923</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>113.71</v>
+        <v>56.51</v>
       </c>
       <c r="B151" t="n">
-        <v>25705</v>
+        <v>20820</v>
       </c>
       <c r="C151" t="n">
-        <v>114.76</v>
+        <v>54.87</v>
       </c>
       <c r="D151" t="n">
-        <v>11220</v>
+        <v>11941</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>103.71</v>
+        <v>57.1</v>
       </c>
       <c r="B152" t="n">
-        <v>49213</v>
+        <v>19457</v>
       </c>
       <c r="C152" t="n">
-        <v>107.01</v>
+        <v>64.23</v>
       </c>
       <c r="D152" t="n">
-        <v>10320</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>96.65000000000001</v>
+        <v>57.17</v>
       </c>
       <c r="B153" t="n">
-        <v>39619</v>
+        <v>18238</v>
       </c>
       <c r="C153" t="n">
-        <v>93.52</v>
+        <v>53.4</v>
       </c>
       <c r="D153" t="n">
-        <v>11315</v>
+        <v>18898</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>104.77</v>
+        <v>57.61</v>
       </c>
       <c r="B154" t="n">
-        <v>46780</v>
+        <v>21001</v>
       </c>
       <c r="C154" t="n">
-        <v>100.16</v>
+        <v>62.94</v>
       </c>
       <c r="D154" t="n">
-        <v>26957</v>
+        <v>11817</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>102.94</v>
+        <v>57.74</v>
       </c>
       <c r="B155" t="n">
-        <v>48267</v>
+        <v>21482</v>
       </c>
       <c r="C155" t="n">
-        <v>105.36</v>
+        <v>51.39</v>
       </c>
       <c r="D155" t="n">
-        <v>12184</v>
+        <v>29886</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>105.67</v>
+        <v>57.79</v>
       </c>
       <c r="B156" t="n">
-        <v>43162</v>
+        <v>23016</v>
       </c>
       <c r="C156" t="n">
-        <v>110.14</v>
+        <v>51.63</v>
       </c>
       <c r="D156" t="n">
-        <v>22001</v>
+        <v>19088</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>104.12</v>
+        <v>58.2</v>
       </c>
       <c r="B157" t="n">
-        <v>44292</v>
+        <v>22433</v>
       </c>
       <c r="C157" t="n">
-        <v>102.43</v>
+        <v>54.44</v>
       </c>
       <c r="D157" t="n">
-        <v>13077</v>
+        <v>20746</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>104.11</v>
+        <v>58.46</v>
       </c>
       <c r="B158" t="n">
-        <v>47048</v>
+        <v>22094</v>
       </c>
       <c r="C158" t="n">
-        <v>107.47</v>
+        <v>57.89</v>
       </c>
       <c r="D158" t="n">
-        <v>23192</v>
+        <v>23965</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>90.93000000000001</v>
+        <v>58.83</v>
       </c>
       <c r="B159" t="n">
-        <v>25172</v>
+        <v>21040</v>
       </c>
       <c r="C159" t="n">
-        <v>91.03</v>
+        <v>58.75</v>
       </c>
       <c r="D159" t="n">
-        <v>17259</v>
+        <v>12844</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>103.26</v>
+        <v>58.88</v>
       </c>
       <c r="B160" t="n">
-        <v>44974</v>
+        <v>21630</v>
       </c>
       <c r="C160" t="n">
-        <v>106.73</v>
+        <v>53.38</v>
       </c>
       <c r="D160" t="n">
-        <v>10006</v>
+        <v>24645</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>148.03</v>
+        <v>59.12</v>
       </c>
       <c r="B161" t="n">
-        <v>21462</v>
+        <v>20082</v>
       </c>
       <c r="C161" t="n">
-        <v>150.65</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="D161" t="n">
-        <v>10740</v>
+        <v>20352</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>110.13</v>
+        <v>59.45</v>
       </c>
       <c r="B162" t="n">
-        <v>31614</v>
+        <v>18408</v>
       </c>
       <c r="C162" t="n">
-        <v>108.12</v>
+        <v>44.52</v>
       </c>
       <c r="D162" t="n">
-        <v>25781</v>
+        <v>24086</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>107.15</v>
+        <v>59.52</v>
       </c>
       <c r="B163" t="n">
-        <v>42775</v>
+        <v>20970</v>
       </c>
       <c r="C163" t="n">
-        <v>107.39</v>
+        <v>63.27</v>
       </c>
       <c r="D163" t="n">
-        <v>26384</v>
+        <v>24952</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>105.54</v>
+        <v>59.62</v>
       </c>
       <c r="B164" t="n">
-        <v>45003</v>
+        <v>20727</v>
       </c>
       <c r="C164" t="n">
-        <v>107.24</v>
+        <v>59.82</v>
       </c>
       <c r="D164" t="n">
-        <v>29882</v>
+        <v>27259</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>42.42</v>
+        <v>59.82</v>
       </c>
       <c r="B165" t="n">
-        <v>24966</v>
+        <v>21665</v>
       </c>
       <c r="C165" t="n">
-        <v>40.49</v>
+        <v>42.25</v>
       </c>
       <c r="D165" t="n">
-        <v>25417</v>
+        <v>13169</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>91.20999999999999</v>
+        <v>59.83</v>
       </c>
       <c r="B166" t="n">
-        <v>24106</v>
+        <v>22432</v>
       </c>
       <c r="C166" t="n">
-        <v>90.91</v>
+        <v>70.94</v>
       </c>
       <c r="D166" t="n">
-        <v>29139</v>
+        <v>21003</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>99.79000000000001</v>
+        <v>59.94</v>
       </c>
       <c r="B167" t="n">
-        <v>43695</v>
+        <v>20741</v>
       </c>
       <c r="C167" t="n">
-        <v>99.75</v>
+        <v>48</v>
       </c>
       <c r="D167" t="n">
-        <v>14471</v>
+        <v>26892</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>113.69</v>
+        <v>60.24</v>
       </c>
       <c r="B168" t="n">
-        <v>22255</v>
+        <v>20521</v>
       </c>
       <c r="C168" t="n">
-        <v>114.01</v>
+        <v>60.32</v>
       </c>
       <c r="D168" t="n">
-        <v>19126</v>
+        <v>25829</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>111.06</v>
+        <v>60.52</v>
       </c>
       <c r="B169" t="n">
-        <v>27693</v>
+        <v>18690</v>
       </c>
       <c r="C169" t="n">
-        <v>113.64</v>
+        <v>47.45</v>
       </c>
       <c r="D169" t="n">
-        <v>13456</v>
+        <v>13626</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>98.33</v>
+        <v>61</v>
       </c>
       <c r="B170" t="n">
-        <v>40912</v>
+        <v>20677</v>
       </c>
       <c r="C170" t="n">
-        <v>100.62</v>
+        <v>48.09</v>
       </c>
       <c r="D170" t="n">
-        <v>15052</v>
+        <v>22438</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>96.44</v>
+        <v>61.22</v>
       </c>
       <c r="B171" t="n">
-        <v>37391</v>
+        <v>20292</v>
       </c>
       <c r="C171" t="n">
-        <v>99.56</v>
+        <v>67.56</v>
       </c>
       <c r="D171" t="n">
-        <v>23378</v>
+        <v>18565</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>103.61</v>
+        <v>61.5</v>
       </c>
       <c r="B172" t="n">
-        <v>46861</v>
+        <v>19564</v>
       </c>
       <c r="C172" t="n">
-        <v>103.58</v>
+        <v>49.77</v>
       </c>
       <c r="D172" t="n">
-        <v>18442</v>
+        <v>23699</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>100.12</v>
+        <v>61.66</v>
       </c>
       <c r="B173" t="n">
-        <v>45686</v>
+        <v>20103</v>
       </c>
       <c r="C173" t="n">
-        <v>102.62</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="D173" t="n">
-        <v>24358</v>
+        <v>28561</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>111.74</v>
+        <v>62.21</v>
       </c>
       <c r="B174" t="n">
-        <v>24937</v>
+        <v>22037</v>
       </c>
       <c r="C174" t="n">
-        <v>109.95</v>
+        <v>59.89</v>
       </c>
       <c r="D174" t="n">
-        <v>14361</v>
+        <v>29265</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>111.84</v>
+        <v>62.39</v>
       </c>
       <c r="B175" t="n">
-        <v>27119</v>
+        <v>20894</v>
       </c>
       <c r="C175" t="n">
-        <v>108.6</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="D175" t="n">
-        <v>21061</v>
+        <v>24053</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>112.9</v>
+        <v>62.82</v>
       </c>
       <c r="B176" t="n">
-        <v>25467</v>
+        <v>20274</v>
       </c>
       <c r="C176" t="n">
-        <v>117.3</v>
+        <v>47.16</v>
       </c>
       <c r="D176" t="n">
-        <v>18522</v>
+        <v>22236</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>96.02</v>
+        <v>62.82</v>
       </c>
       <c r="B177" t="n">
-        <v>36097</v>
+        <v>20285</v>
       </c>
       <c r="C177" t="n">
-        <v>96.48</v>
+        <v>75.69</v>
       </c>
       <c r="D177" t="n">
-        <v>29613</v>
+        <v>23182</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>163.73</v>
+        <v>63.43</v>
       </c>
       <c r="B178" t="n">
-        <v>22798</v>
+        <v>21310</v>
       </c>
       <c r="C178" t="n">
-        <v>167.38</v>
+        <v>61.27</v>
       </c>
       <c r="D178" t="n">
-        <v>23179</v>
+        <v>20212</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>62.14</v>
+        <v>63.67</v>
       </c>
       <c r="B179" t="n">
-        <v>25590</v>
+        <v>20803</v>
       </c>
       <c r="C179" t="n">
-        <v>61.67</v>
+        <v>62.25</v>
       </c>
       <c r="D179" t="n">
-        <v>20440</v>
+        <v>28006</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>145</v>
+        <v>64.05</v>
       </c>
       <c r="B180" t="n">
-        <v>25157</v>
+        <v>21216</v>
       </c>
       <c r="C180" t="n">
-        <v>143.59</v>
+        <v>69.19</v>
       </c>
       <c r="D180" t="n">
-        <v>29293</v>
+        <v>25004</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>94.09999999999999</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="B181" t="n">
-        <v>30171</v>
+        <v>20783</v>
       </c>
       <c r="C181" t="n">
-        <v>93.12</v>
+        <v>63.87</v>
       </c>
       <c r="D181" t="n">
-        <v>24703</v>
+        <v>23740</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>109.7</v>
+        <v>64.36</v>
       </c>
       <c r="B182" t="n">
-        <v>31061</v>
+        <v>20917</v>
       </c>
       <c r="C182" t="n">
-        <v>114.3</v>
+        <v>73.11</v>
       </c>
       <c r="D182" t="n">
-        <v>18037</v>
+        <v>27914</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>100.83</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="B183" t="n">
-        <v>45653</v>
+        <v>20826</v>
       </c>
       <c r="C183" t="n">
-        <v>103.09</v>
+        <v>54.3</v>
       </c>
       <c r="D183" t="n">
-        <v>19520</v>
+        <v>23346</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>112.92</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="B184" t="n">
-        <v>24278</v>
+        <v>20791</v>
       </c>
       <c r="C184" t="n">
-        <v>116.09</v>
+        <v>52.17</v>
       </c>
       <c r="D184" t="n">
-        <v>19660</v>
+        <v>11360</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>7.16</v>
+        <v>65.33</v>
       </c>
       <c r="B185" t="n">
-        <v>26152</v>
+        <v>22067</v>
       </c>
       <c r="C185" t="n">
-        <v>8.01</v>
+        <v>56.47</v>
       </c>
       <c r="D185" t="n">
-        <v>10574</v>
+        <v>23470</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>93.31999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="B186" t="n">
-        <v>31005</v>
+        <v>21463</v>
       </c>
       <c r="C186" t="n">
-        <v>92.92</v>
+        <v>60.12</v>
       </c>
       <c r="D186" t="n">
-        <v>16123</v>
+        <v>13061</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>95.3</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="B187" t="n">
-        <v>34636</v>
+        <v>22023</v>
       </c>
       <c r="C187" t="n">
-        <v>98.12</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="D187" t="n">
-        <v>22939</v>
+        <v>25469</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>113.18</v>
+        <v>65.83</v>
       </c>
       <c r="B188" t="n">
-        <v>23135</v>
+        <v>20137</v>
       </c>
       <c r="C188" t="n">
-        <v>113.14</v>
+        <v>78.75</v>
       </c>
       <c r="D188" t="n">
-        <v>25307</v>
+        <v>21708</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>94.95999999999999</v>
+        <v>65.94</v>
       </c>
       <c r="B189" t="n">
-        <v>33712</v>
+        <v>20294</v>
       </c>
       <c r="C189" t="n">
-        <v>98.59999999999999</v>
+        <v>65.55</v>
       </c>
       <c r="D189" t="n">
-        <v>24877</v>
+        <v>18283</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>90.08</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="B190" t="n">
-        <v>23624</v>
+        <v>19890</v>
       </c>
       <c r="C190" t="n">
-        <v>92.29000000000001</v>
+        <v>72.97</v>
       </c>
       <c r="D190" t="n">
-        <v>10171</v>
+        <v>22032</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>113.05</v>
+        <v>66.06</v>
       </c>
       <c r="B191" t="n">
-        <v>25530</v>
+        <v>19710</v>
       </c>
       <c r="C191" t="n">
-        <v>117.28</v>
+        <v>54.51</v>
       </c>
       <c r="D191" t="n">
-        <v>21601</v>
+        <v>23705</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>101.08</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="B192" t="n">
-        <v>47218</v>
+        <v>20099</v>
       </c>
       <c r="C192" t="n">
-        <v>97.75</v>
+        <v>73.12</v>
       </c>
       <c r="D192" t="n">
-        <v>13901</v>
+        <v>21851</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>113.96</v>
+        <v>66.37</v>
       </c>
       <c r="B193" t="n">
-        <v>25795</v>
+        <v>19876</v>
       </c>
       <c r="C193" t="n">
-        <v>117.74</v>
+        <v>51.4</v>
       </c>
       <c r="D193" t="n">
-        <v>23975</v>
+        <v>19752</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>145.96</v>
+        <v>66.88</v>
       </c>
       <c r="B194" t="n">
-        <v>24394</v>
+        <v>21071</v>
       </c>
       <c r="C194" t="n">
-        <v>140.99</v>
+        <v>68.16</v>
       </c>
       <c r="D194" t="n">
-        <v>29306</v>
+        <v>25014</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>78.66</v>
+        <v>67.08</v>
       </c>
       <c r="B195" t="n">
-        <v>23202</v>
+        <v>20843</v>
       </c>
       <c r="C195" t="n">
-        <v>82.47</v>
+        <v>63.08</v>
       </c>
       <c r="D195" t="n">
-        <v>22267</v>
+        <v>28894</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>105.25</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="B196" t="n">
-        <v>45553</v>
+        <v>20845</v>
       </c>
       <c r="C196" t="n">
-        <v>107.27</v>
+        <v>66.98</v>
       </c>
       <c r="D196" t="n">
-        <v>14994</v>
+        <v>14688</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>98.52</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="B197" t="n">
-        <v>40996</v>
+        <v>20361</v>
       </c>
       <c r="C197" t="n">
-        <v>101.54</v>
+        <v>75.55</v>
       </c>
       <c r="D197" t="n">
-        <v>27305</v>
+        <v>20265</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>98.51000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="B198" t="n">
-        <v>43267</v>
+        <v>19884</v>
       </c>
       <c r="C198" t="n">
-        <v>95.65000000000001</v>
+        <v>54.61</v>
       </c>
       <c r="D198" t="n">
-        <v>24038</v>
+        <v>12777</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>53.71</v>
+        <v>67.81</v>
       </c>
       <c r="B199" t="n">
-        <v>23996</v>
+        <v>19461</v>
       </c>
       <c r="C199" t="n">
-        <v>53.06</v>
+        <v>77.09</v>
       </c>
       <c r="D199" t="n">
-        <v>29408</v>
+        <v>24226</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>95.61</v>
+        <v>68.03</v>
       </c>
       <c r="B200" t="n">
-        <v>36283</v>
+        <v>21473</v>
       </c>
       <c r="C200" t="n">
-        <v>92.69</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="D200" t="n">
-        <v>25072</v>
+        <v>16740</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>111.06</v>
+        <v>68.34</v>
       </c>
       <c r="B201" t="n">
-        <v>28350</v>
+        <v>21404</v>
       </c>
       <c r="C201" t="n">
-        <v>113.51</v>
+        <v>84.16</v>
       </c>
       <c r="D201" t="n">
-        <v>18843</v>
+        <v>23466</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>98.98</v>
+        <v>68.62</v>
       </c>
       <c r="B202" t="n">
-        <v>43167</v>
+        <v>20540</v>
       </c>
       <c r="C202" t="n">
-        <v>100.43</v>
+        <v>61.5</v>
       </c>
       <c r="D202" t="n">
-        <v>11978</v>
+        <v>15296</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>90.44</v>
+        <v>69.03</v>
       </c>
       <c r="B203" t="n">
-        <v>25783</v>
+        <v>20621</v>
       </c>
       <c r="C203" t="n">
-        <v>92.39</v>
+        <v>75.73</v>
       </c>
       <c r="D203" t="n">
-        <v>17383</v>
+        <v>20466</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>94.02</v>
+        <v>69.75</v>
       </c>
       <c r="B204" t="n">
-        <v>29819</v>
+        <v>21699</v>
       </c>
       <c r="C204" t="n">
-        <v>93.5</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="D204" t="n">
-        <v>19897</v>
+        <v>18853</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>58.84</v>
+        <v>71.03</v>
       </c>
       <c r="B205" t="n">
-        <v>23779</v>
+        <v>21085</v>
       </c>
       <c r="C205" t="n">
-        <v>60.86</v>
+        <v>58.89</v>
       </c>
       <c r="D205" t="n">
-        <v>16777</v>
+        <v>15264</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>92.92</v>
+        <v>71.2</v>
       </c>
       <c r="B206" t="n">
-        <v>27954</v>
+        <v>21633</v>
       </c>
       <c r="C206" t="n">
-        <v>90.19</v>
+        <v>71.61</v>
       </c>
       <c r="D206" t="n">
-        <v>17883</v>
+        <v>16605</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>92.09</v>
+        <v>71.83</v>
       </c>
       <c r="B207" t="n">
-        <v>25738</v>
+        <v>19633</v>
       </c>
       <c r="C207" t="n">
-        <v>89.89</v>
+        <v>75.64</v>
       </c>
       <c r="D207" t="n">
-        <v>23357</v>
+        <v>11558</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>121.03</v>
+        <v>72.34</v>
       </c>
       <c r="B208" t="n">
-        <v>24578</v>
+        <v>20929</v>
       </c>
       <c r="C208" t="n">
-        <v>123.41</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="D208" t="n">
-        <v>22379</v>
+        <v>27585</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>91.54000000000001</v>
+        <v>72.61</v>
       </c>
       <c r="B209" t="n">
-        <v>26821</v>
+        <v>21003</v>
       </c>
       <c r="C209" t="n">
-        <v>93.45999999999999</v>
+        <v>75.23</v>
       </c>
       <c r="D209" t="n">
-        <v>13029</v>
+        <v>13239</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>102.28</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="B210" t="n">
-        <v>46053</v>
+        <v>20348</v>
       </c>
       <c r="C210" t="n">
-        <v>103.81</v>
+        <v>85.12</v>
       </c>
       <c r="D210" t="n">
-        <v>13252</v>
+        <v>22122</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>92.92</v>
+        <v>73.56</v>
       </c>
       <c r="B211" t="n">
-        <v>26932</v>
+        <v>23143</v>
       </c>
       <c r="C211" t="n">
-        <v>90.17</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="D211" t="n">
-        <v>16407</v>
+        <v>12204</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>100.15</v>
+        <v>73.64</v>
       </c>
       <c r="B212" t="n">
-        <v>46482</v>
+        <v>21067</v>
       </c>
       <c r="C212" t="n">
-        <v>100.27</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="D212" t="n">
-        <v>12197</v>
+        <v>22640</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>108.01</v>
+        <v>74.59</v>
       </c>
       <c r="B213" t="n">
-        <v>37762</v>
+        <v>19877</v>
       </c>
       <c r="C213" t="n">
-        <v>104.31</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="D213" t="n">
-        <v>18582</v>
+        <v>29446</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>90.73</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="B214" t="n">
-        <v>21308</v>
+        <v>20839</v>
       </c>
       <c r="C214" t="n">
-        <v>92.61</v>
+        <v>82.39</v>
       </c>
       <c r="D214" t="n">
-        <v>18453</v>
+        <v>29032</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>168.33</v>
+        <v>74.81</v>
       </c>
       <c r="B215" t="n">
-        <v>23817</v>
+        <v>20976</v>
       </c>
       <c r="C215" t="n">
-        <v>161.97</v>
+        <v>68.42</v>
       </c>
       <c r="D215" t="n">
-        <v>14031</v>
+        <v>27237</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>94.13</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="B216" t="n">
-        <v>30192</v>
+        <v>20812</v>
       </c>
       <c r="C216" t="n">
-        <v>93.14</v>
+        <v>56.23</v>
       </c>
       <c r="D216" t="n">
-        <v>27424</v>
+        <v>19734</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>92.87</v>
+        <v>76.05</v>
       </c>
       <c r="B217" t="n">
-        <v>27794</v>
+        <v>21010</v>
       </c>
       <c r="C217" t="n">
-        <v>88.58</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="D217" t="n">
-        <v>19600</v>
+        <v>24366</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>111.64</v>
+        <v>76.09</v>
       </c>
       <c r="B218" t="n">
-        <v>30331</v>
+        <v>20932</v>
       </c>
       <c r="C218" t="n">
-        <v>113.34</v>
+        <v>87.22</v>
       </c>
       <c r="D218" t="n">
-        <v>28026</v>
+        <v>13186</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>97</v>
+        <v>76.28</v>
       </c>
       <c r="B219" t="n">
-        <v>38254</v>
+        <v>19565</v>
       </c>
       <c r="C219" t="n">
-        <v>93.52</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D219" t="n">
-        <v>21011</v>
+        <v>27240</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>77.40000000000001</v>
+        <v>76.56</v>
       </c>
       <c r="B220" t="n">
-        <v>24491</v>
+        <v>20083</v>
       </c>
       <c r="C220" t="n">
-        <v>79.51000000000001</v>
+        <v>63.98</v>
       </c>
       <c r="D220" t="n">
-        <v>15125</v>
+        <v>24920</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>101.86</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="B221" t="n">
-        <v>46114</v>
+        <v>20686</v>
       </c>
       <c r="C221" t="n">
-        <v>106.07</v>
+        <v>82.78</v>
       </c>
       <c r="D221" t="n">
-        <v>17398</v>
+        <v>21329</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>174.38</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="B222" t="n">
-        <v>23338</v>
+        <v>19621</v>
       </c>
       <c r="C222" t="n">
-        <v>171.63</v>
+        <v>62.58</v>
       </c>
       <c r="D222" t="n">
-        <v>28660</v>
+        <v>11079</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>93.77</v>
+        <v>77.52</v>
       </c>
       <c r="B223" t="n">
-        <v>30077</v>
+        <v>19984</v>
       </c>
       <c r="C223" t="n">
-        <v>93.52</v>
+        <v>80.03</v>
       </c>
       <c r="D223" t="n">
-        <v>10580</v>
+        <v>22628</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>110.83</v>
+        <v>78.84</v>
       </c>
       <c r="B224" t="n">
-        <v>29304</v>
+        <v>19586</v>
       </c>
       <c r="C224" t="n">
-        <v>106.36</v>
+        <v>84.3</v>
       </c>
       <c r="D224" t="n">
-        <v>19326</v>
+        <v>15019</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>94.20999999999999</v>
+        <v>78.91</v>
       </c>
       <c r="B225" t="n">
-        <v>30700</v>
+        <v>20170</v>
       </c>
       <c r="C225" t="n">
-        <v>90.62</v>
+        <v>66.58</v>
       </c>
       <c r="D225" t="n">
-        <v>10761</v>
+        <v>11253</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>97.28</v>
+        <v>79.05</v>
       </c>
       <c r="B226" t="n">
-        <v>39809</v>
+        <v>21795</v>
       </c>
       <c r="C226" t="n">
-        <v>93.31999999999999</v>
+        <v>84.02</v>
       </c>
       <c r="D226" t="n">
-        <v>11921</v>
+        <v>24619</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>96.89</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="B227" t="n">
-        <v>39585</v>
+        <v>20459</v>
       </c>
       <c r="C227" t="n">
-        <v>98.72</v>
+        <v>74.66</v>
       </c>
       <c r="D227" t="n">
-        <v>15396</v>
+        <v>20465</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>94.51000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="B228" t="n">
-        <v>31644</v>
+        <v>20745</v>
       </c>
       <c r="C228" t="n">
-        <v>91.87</v>
+        <v>70.42</v>
       </c>
       <c r="D228" t="n">
-        <v>29907</v>
+        <v>24498</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>106.48</v>
+        <v>80.25</v>
       </c>
       <c r="B229" t="n">
-        <v>43042</v>
+        <v>20139</v>
       </c>
       <c r="C229" t="n">
-        <v>103.66</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="D229" t="n">
-        <v>19893</v>
+        <v>25156</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>92.39</v>
+        <v>80.41</v>
       </c>
       <c r="B230" t="n">
-        <v>26793</v>
+        <v>20403</v>
       </c>
       <c r="C230" t="n">
-        <v>93.34</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="D230" t="n">
-        <v>19999</v>
+        <v>14515</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>110.15</v>
+        <v>83.34</v>
       </c>
       <c r="B231" t="n">
-        <v>30091</v>
+        <v>20871</v>
       </c>
       <c r="C231" t="n">
-        <v>112.39</v>
+        <v>89.55</v>
       </c>
       <c r="D231" t="n">
-        <v>17538</v>
+        <v>24803</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>107.76</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="B232" t="n">
-        <v>39133</v>
+        <v>20179</v>
       </c>
       <c r="C232" t="n">
-        <v>103.16</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="D232" t="n">
-        <v>20423</v>
+        <v>12615</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>92.48</v>
+        <v>83.86</v>
       </c>
       <c r="B233" t="n">
-        <v>25961</v>
+        <v>20309</v>
       </c>
       <c r="C233" t="n">
-        <v>94.77</v>
+        <v>79.81</v>
       </c>
       <c r="D233" t="n">
-        <v>21189</v>
+        <v>24537</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>178.48</v>
+        <v>83.95</v>
       </c>
       <c r="B234" t="n">
-        <v>22427</v>
+        <v>20021</v>
       </c>
       <c r="C234" t="n">
-        <v>180</v>
+        <v>87.41</v>
       </c>
       <c r="D234" t="n">
-        <v>22416</v>
+        <v>14264</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>90.18000000000001</v>
+        <v>84.08</v>
       </c>
       <c r="B235" t="n">
-        <v>21335</v>
+        <v>20078</v>
       </c>
       <c r="C235" t="n">
-        <v>87.04000000000001</v>
+        <v>91.48</v>
       </c>
       <c r="D235" t="n">
-        <v>19796</v>
+        <v>17464</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>80.17</v>
+        <v>84.41</v>
       </c>
       <c r="B236" t="n">
-        <v>24823</v>
+        <v>20767</v>
       </c>
       <c r="C236" t="n">
-        <v>77.42</v>
+        <v>93.63</v>
       </c>
       <c r="D236" t="n">
-        <v>18891</v>
+        <v>27307</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>107.92</v>
+        <v>84.98</v>
       </c>
       <c r="B237" t="n">
-        <v>38318</v>
+        <v>20490</v>
       </c>
       <c r="C237" t="n">
-        <v>104.59</v>
+        <v>73.98</v>
       </c>
       <c r="D237" t="n">
-        <v>29857</v>
+        <v>27335</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>88.69</v>
+        <v>87.38</v>
       </c>
       <c r="B238" t="n">
-        <v>24367</v>
+        <v>20112</v>
       </c>
       <c r="C238" t="n">
-        <v>88.16</v>
+        <v>104.08</v>
       </c>
       <c r="D238" t="n">
-        <v>26540</v>
+        <v>21392</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>108.65</v>
+        <v>87.91</v>
       </c>
       <c r="B239" t="n">
-        <v>37617</v>
+        <v>20456</v>
       </c>
       <c r="C239" t="n">
-        <v>112.44</v>
+        <v>107.04</v>
       </c>
       <c r="D239" t="n">
-        <v>11177</v>
+        <v>13384</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>103.29</v>
+        <v>87.95</v>
       </c>
       <c r="B240" t="n">
-        <v>47435</v>
+        <v>21161</v>
       </c>
       <c r="C240" t="n">
-        <v>104.16</v>
+        <v>106.11</v>
       </c>
       <c r="D240" t="n">
-        <v>25909</v>
+        <v>14015</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>96.68000000000001</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="B241" t="n">
-        <v>36902</v>
+        <v>19782</v>
       </c>
       <c r="C241" t="n">
-        <v>96.94</v>
+        <v>85.69</v>
       </c>
       <c r="D241" t="n">
-        <v>14175</v>
+        <v>14811</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>101.53</v>
+        <v>88.17</v>
       </c>
       <c r="B242" t="n">
-        <v>46320</v>
+        <v>20639</v>
       </c>
       <c r="C242" t="n">
-        <v>101.26</v>
+        <v>74.63</v>
       </c>
       <c r="D242" t="n">
-        <v>10008</v>
+        <v>24214</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>100.6</v>
+        <v>88.17</v>
       </c>
       <c r="B243" t="n">
-        <v>44359</v>
+        <v>20289</v>
       </c>
       <c r="C243" t="n">
-        <v>103.26</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="D243" t="n">
-        <v>11065</v>
+        <v>24884</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>106.01</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="B244" t="n">
-        <v>42695</v>
+        <v>20913</v>
       </c>
       <c r="C244" t="n">
-        <v>105.02</v>
+        <v>63.99</v>
       </c>
       <c r="D244" t="n">
-        <v>28793</v>
+        <v>22778</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>99.65000000000001</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="B245" t="n">
-        <v>43853</v>
+        <v>21098</v>
       </c>
       <c r="C245" t="n">
-        <v>98.13</v>
+        <v>82.19</v>
       </c>
       <c r="D245" t="n">
-        <v>19808</v>
+        <v>10272</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>110.69</v>
+        <v>89.16</v>
       </c>
       <c r="B246" t="n">
-        <v>28734</v>
+        <v>20810</v>
       </c>
       <c r="C246" t="n">
-        <v>112.7</v>
+        <v>99.13</v>
       </c>
       <c r="D246" t="n">
-        <v>10159</v>
+        <v>15869</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>104.21</v>
+        <v>89.36</v>
       </c>
       <c r="B247" t="n">
-        <v>47357</v>
+        <v>21323</v>
       </c>
       <c r="C247" t="n">
-        <v>106.42</v>
+        <v>99.02</v>
       </c>
       <c r="D247" t="n">
-        <v>27874</v>
+        <v>22442</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>40.5</v>
+        <v>89.63</v>
       </c>
       <c r="B248" t="n">
-        <v>22353</v>
+        <v>20576</v>
       </c>
       <c r="C248" t="n">
-        <v>41.22</v>
+        <v>83.62</v>
       </c>
       <c r="D248" t="n">
-        <v>22039</v>
+        <v>11840</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>110.59</v>
+        <v>89.98</v>
       </c>
       <c r="B249" t="n">
-        <v>30332</v>
+        <v>21670</v>
       </c>
       <c r="C249" t="n">
-        <v>108.4</v>
+        <v>88.62</v>
       </c>
       <c r="D249" t="n">
-        <v>25575</v>
+        <v>16160</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>107.86</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="B250" t="n">
-        <v>37560</v>
+        <v>20353</v>
       </c>
       <c r="C250" t="n">
-        <v>105.62</v>
+        <v>97.14</v>
       </c>
       <c r="D250" t="n">
-        <v>20801</v>
+        <v>21758</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>107.25</v>
+        <v>90.34</v>
       </c>
       <c r="B251" t="n">
-        <v>40116</v>
+        <v>20469</v>
       </c>
       <c r="C251" t="n">
-        <v>103.29</v>
+        <v>74.22</v>
       </c>
       <c r="D251" t="n">
-        <v>27827</v>
+        <v>15210</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>103.52</v>
+        <v>90.89</v>
       </c>
       <c r="B252" t="n">
-        <v>46933</v>
+        <v>21026</v>
       </c>
       <c r="C252" t="n">
-        <v>101.53</v>
+        <v>66.97</v>
       </c>
       <c r="D252" t="n">
-        <v>17502</v>
+        <v>26046</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>108.52</v>
+        <v>90.92</v>
       </c>
       <c r="B253" t="n">
-        <v>37808</v>
+        <v>21584</v>
       </c>
       <c r="C253" t="n">
-        <v>111.91</v>
+        <v>95.84</v>
       </c>
       <c r="D253" t="n">
-        <v>11853</v>
+        <v>29639</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>144.57</v>
+        <v>91.81</v>
       </c>
       <c r="B254" t="n">
-        <v>23721</v>
+        <v>21806</v>
       </c>
       <c r="C254" t="n">
-        <v>149.99</v>
+        <v>75.34</v>
       </c>
       <c r="D254" t="n">
-        <v>12106</v>
+        <v>10979</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>114.1</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="B255" t="n">
-        <v>23041</v>
+        <v>22091</v>
       </c>
       <c r="C255" t="n">
-        <v>116.14</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="D255" t="n">
-        <v>14536</v>
+        <v>19902</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>157.62</v>
+        <v>92.59</v>
       </c>
       <c r="B256" t="n">
-        <v>22630</v>
+        <v>21844</v>
       </c>
       <c r="C256" t="n">
-        <v>160.24</v>
+        <v>95.78</v>
       </c>
       <c r="D256" t="n">
-        <v>17925</v>
+        <v>10558</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>107.95</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="B257" t="n">
-        <v>38892</v>
+        <v>22216</v>
       </c>
       <c r="C257" t="n">
-        <v>108.81</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="D257" t="n">
-        <v>12762</v>
+        <v>13206</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>107.74</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="B258" t="n">
-        <v>43039</v>
+        <v>21863</v>
       </c>
       <c r="C258" t="n">
-        <v>104.74</v>
+        <v>101.09</v>
       </c>
       <c r="D258" t="n">
-        <v>17011</v>
+        <v>18304</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>101.5</v>
+        <v>92.8</v>
       </c>
       <c r="B259" t="n">
-        <v>46970</v>
+        <v>22283</v>
       </c>
       <c r="C259" t="n">
-        <v>98.25</v>
+        <v>110.61</v>
       </c>
       <c r="D259" t="n">
-        <v>11885</v>
+        <v>22714</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>90.98999999999999</v>
+        <v>92.81</v>
       </c>
       <c r="B260" t="n">
-        <v>24702</v>
+        <v>20894</v>
       </c>
       <c r="C260" t="n">
-        <v>90.90000000000001</v>
+        <v>110.38</v>
       </c>
       <c r="D260" t="n">
-        <v>16016</v>
+        <v>25404</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>93</v>
+        <v>92.88</v>
       </c>
       <c r="B261" t="n">
-        <v>30048</v>
+        <v>22485</v>
       </c>
       <c r="C261" t="n">
-        <v>92.40000000000001</v>
+        <v>77.11</v>
       </c>
       <c r="D261" t="n">
-        <v>15296</v>
+        <v>12360</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>109.07</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="B262" t="n">
-        <v>36534</v>
+        <v>23469</v>
       </c>
       <c r="C262" t="n">
-        <v>110.2</v>
+        <v>118.42</v>
       </c>
       <c r="D262" t="n">
-        <v>20536</v>
+        <v>12652</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>111.69</v>
+        <v>93.11</v>
       </c>
       <c r="B263" t="n">
-        <v>25994</v>
+        <v>22382</v>
       </c>
       <c r="C263" t="n">
-        <v>114.84</v>
+        <v>106.9</v>
       </c>
       <c r="D263" t="n">
-        <v>15488</v>
+        <v>23343</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>113.03</v>
+        <v>93.5</v>
       </c>
       <c r="B264" t="n">
-        <v>25618</v>
+        <v>22571</v>
       </c>
       <c r="C264" t="n">
-        <v>113.67</v>
+        <v>97.77</v>
       </c>
       <c r="D264" t="n">
-        <v>10675</v>
+        <v>17241</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>76.26000000000001</v>
+        <v>94.16</v>
       </c>
       <c r="B265" t="n">
-        <v>24340</v>
+        <v>24014</v>
       </c>
       <c r="C265" t="n">
-        <v>76.52</v>
+        <v>111.97</v>
       </c>
       <c r="D265" t="n">
-        <v>13356</v>
+        <v>19882</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>109.7</v>
+        <v>94.84</v>
       </c>
       <c r="B266" t="n">
-        <v>30947</v>
+        <v>24338</v>
       </c>
       <c r="C266" t="n">
-        <v>112.38</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="D266" t="n">
-        <v>28541</v>
+        <v>28127</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>103.43</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="B267" t="n">
-        <v>47755</v>
+        <v>25114</v>
       </c>
       <c r="C267" t="n">
-        <v>105.3</v>
+        <v>106.32</v>
       </c>
       <c r="D267" t="n">
-        <v>26938</v>
+        <v>11109</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>114.84</v>
+        <v>95.28</v>
       </c>
       <c r="B268" t="n">
-        <v>21979</v>
+        <v>26453</v>
       </c>
       <c r="C268" t="n">
-        <v>118.42</v>
+        <v>120.21</v>
       </c>
       <c r="D268" t="n">
-        <v>23585</v>
+        <v>29013</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>103.32</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="B269" t="n">
-        <v>48071</v>
+        <v>25999</v>
       </c>
       <c r="C269" t="n">
-        <v>103.43</v>
+        <v>113.46</v>
       </c>
       <c r="D269" t="n">
-        <v>27840</v>
+        <v>20715</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>99.02</v>
+        <v>95.66</v>
       </c>
       <c r="B270" t="n">
-        <v>43491</v>
+        <v>26962</v>
       </c>
       <c r="C270" t="n">
-        <v>96.33</v>
+        <v>104.28</v>
       </c>
       <c r="D270" t="n">
-        <v>24762</v>
+        <v>16793</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>111.52</v>
+        <v>95.86</v>
       </c>
       <c r="B271" t="n">
-        <v>29127</v>
+        <v>26696</v>
       </c>
       <c r="C271" t="n">
-        <v>107.47</v>
+        <v>108.74</v>
       </c>
       <c r="D271" t="n">
-        <v>27639</v>
+        <v>17051</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>101.26</v>
+        <v>95.95</v>
       </c>
       <c r="B272" t="n">
-        <v>47610</v>
+        <v>27260</v>
       </c>
       <c r="C272" t="n">
-        <v>99.39</v>
+        <v>100.19</v>
       </c>
       <c r="D272" t="n">
-        <v>13815</v>
+        <v>24665</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>114.02</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="B273" t="n">
-        <v>24929</v>
+        <v>27921</v>
       </c>
       <c r="C273" t="n">
-        <v>113.4</v>
+        <v>104.38</v>
       </c>
       <c r="D273" t="n">
-        <v>29192</v>
+        <v>12325</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>105.92</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="B274" t="n">
-        <v>46200</v>
+        <v>27989</v>
       </c>
       <c r="C274" t="n">
-        <v>104.63</v>
+        <v>103.35</v>
       </c>
       <c r="D274" t="n">
-        <v>21121</v>
+        <v>27487</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>92.16</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="B275" t="n">
-        <v>29372</v>
+        <v>27291</v>
       </c>
       <c r="C275" t="n">
-        <v>89.65000000000001</v>
+        <v>102.91</v>
       </c>
       <c r="D275" t="n">
-        <v>29415</v>
+        <v>19636</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>97.01000000000001</v>
+        <v>97.44</v>
       </c>
       <c r="B276" t="n">
-        <v>37299</v>
+        <v>29551</v>
       </c>
       <c r="C276" t="n">
-        <v>94.56</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="D276" t="n">
-        <v>29601</v>
+        <v>17941</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>83.42</v>
+        <v>97.52</v>
       </c>
       <c r="B277" t="n">
-        <v>23974</v>
+        <v>29220</v>
       </c>
       <c r="C277" t="n">
-        <v>82.84999999999999</v>
+        <v>101.76</v>
       </c>
       <c r="D277" t="n">
-        <v>21483</v>
+        <v>21705</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>112.34</v>
+        <v>97.86</v>
       </c>
       <c r="B278" t="n">
-        <v>25158</v>
+        <v>30478</v>
       </c>
       <c r="C278" t="n">
-        <v>111.91</v>
+        <v>86.91</v>
       </c>
       <c r="D278" t="n">
-        <v>12570</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>93.38</v>
+        <v>98.72</v>
       </c>
       <c r="B279" t="n">
-        <v>32260</v>
+        <v>32915</v>
       </c>
       <c r="C279" t="n">
-        <v>94.84999999999999</v>
+        <v>85.25</v>
       </c>
       <c r="D279" t="n">
-        <v>29769</v>
+        <v>25505</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>109.11</v>
+        <v>99.13</v>
       </c>
       <c r="B280" t="n">
-        <v>35849</v>
+        <v>34792</v>
       </c>
       <c r="C280" t="n">
-        <v>112.99</v>
+        <v>99.06</v>
       </c>
       <c r="D280" t="n">
-        <v>24950</v>
+        <v>17418</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>55.42</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="B281" t="n">
-        <v>24666</v>
+        <v>35135</v>
       </c>
       <c r="C281" t="n">
-        <v>55.92</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="D281" t="n">
-        <v>25140</v>
+        <v>16336</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>91.39</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="B282" t="n">
-        <v>26864</v>
+        <v>34378</v>
       </c>
       <c r="C282" t="n">
-        <v>88</v>
+        <v>100.77</v>
       </c>
       <c r="D282" t="n">
-        <v>18151</v>
+        <v>17769</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>111.17</v>
+        <v>100.07</v>
       </c>
       <c r="B283" t="n">
-        <v>28678</v>
+        <v>35019</v>
       </c>
       <c r="C283" t="n">
-        <v>113.55</v>
+        <v>105.02</v>
       </c>
       <c r="D283" t="n">
-        <v>28742</v>
+        <v>25577</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>108.86</v>
+        <v>100.23</v>
       </c>
       <c r="B284" t="n">
-        <v>34927</v>
+        <v>35112</v>
       </c>
       <c r="C284" t="n">
-        <v>104.93</v>
+        <v>114.62</v>
       </c>
       <c r="D284" t="n">
-        <v>28867</v>
+        <v>18063</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>127.28</v>
+        <v>100.45</v>
       </c>
       <c r="B285" t="n">
-        <v>23275</v>
+        <v>36834</v>
       </c>
       <c r="C285" t="n">
-        <v>130.6</v>
+        <v>103.75</v>
       </c>
       <c r="D285" t="n">
-        <v>14985</v>
+        <v>12543</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>97.27</v>
+        <v>100.55</v>
       </c>
       <c r="B286" t="n">
-        <v>41506</v>
+        <v>36188</v>
       </c>
       <c r="C286" t="n">
-        <v>93.93000000000001</v>
+        <v>111.11</v>
       </c>
       <c r="D286" t="n">
-        <v>18460</v>
+        <v>24590</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>90.59999999999999</v>
+        <v>100.64</v>
       </c>
       <c r="B287" t="n">
-        <v>24116</v>
+        <v>35829</v>
       </c>
       <c r="C287" t="n">
-        <v>87.52</v>
+        <v>94.5</v>
       </c>
       <c r="D287" t="n">
-        <v>10693</v>
+        <v>11189</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>167.14</v>
+        <v>100.76</v>
       </c>
       <c r="B288" t="n">
-        <v>24245</v>
+        <v>35518</v>
       </c>
       <c r="C288" t="n">
-        <v>172.41</v>
+        <v>105.8</v>
       </c>
       <c r="D288" t="n">
-        <v>26364</v>
+        <v>21509</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>105.82</v>
+        <v>101.01</v>
       </c>
       <c r="B289" t="n">
-        <v>45319</v>
+        <v>36400</v>
       </c>
       <c r="C289" t="n">
-        <v>105.92</v>
+        <v>101.15</v>
       </c>
       <c r="D289" t="n">
-        <v>19783</v>
+        <v>22621</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>104.14</v>
+        <v>101.24</v>
       </c>
       <c r="B290" t="n">
-        <v>47575</v>
+        <v>37672</v>
       </c>
       <c r="C290" t="n">
-        <v>108.2</v>
+        <v>100.25</v>
       </c>
       <c r="D290" t="n">
-        <v>15587</v>
+        <v>17323</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>105.3</v>
+        <v>101.89</v>
       </c>
       <c r="B291" t="n">
-        <v>43241</v>
+        <v>37464</v>
       </c>
       <c r="C291" t="n">
-        <v>105.77</v>
+        <v>95.63</v>
       </c>
       <c r="D291" t="n">
-        <v>14537</v>
+        <v>22229</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>108.2</v>
+        <v>102.24</v>
       </c>
       <c r="B292" t="n">
-        <v>39230</v>
+        <v>37858</v>
       </c>
       <c r="C292" t="n">
-        <v>109.36</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="D292" t="n">
-        <v>14071</v>
+        <v>24360</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>95.33</v>
+        <v>102.27</v>
       </c>
       <c r="B293" t="n">
-        <v>37326</v>
+        <v>38709</v>
       </c>
       <c r="C293" t="n">
-        <v>98.87</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="D293" t="n">
-        <v>11719</v>
+        <v>27406</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>91.76000000000001</v>
+        <v>102.72</v>
       </c>
       <c r="B294" t="n">
-        <v>26155</v>
+        <v>38503</v>
       </c>
       <c r="C294" t="n">
-        <v>92.87</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="D294" t="n">
-        <v>24751</v>
+        <v>27700</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>105.84</v>
+        <v>104.79</v>
       </c>
       <c r="B295" t="n">
-        <v>46439</v>
+        <v>37152</v>
       </c>
       <c r="C295" t="n">
-        <v>104.21</v>
+        <v>87.2</v>
       </c>
       <c r="D295" t="n">
-        <v>21465</v>
+        <v>22762</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>113.17</v>
+        <v>104.9</v>
       </c>
       <c r="B296" t="n">
-        <v>26553</v>
+        <v>36885</v>
       </c>
       <c r="C296" t="n">
-        <v>109.38</v>
+        <v>109.97</v>
       </c>
       <c r="D296" t="n">
-        <v>26519</v>
+        <v>20761</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>106.01</v>
+        <v>105.25</v>
       </c>
       <c r="B297" t="n">
-        <v>41531</v>
+        <v>36572</v>
       </c>
       <c r="C297" t="n">
-        <v>107</v>
+        <v>127.95</v>
       </c>
       <c r="D297" t="n">
-        <v>26968</v>
+        <v>19824</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>114.17</v>
+        <v>106.12</v>
       </c>
       <c r="B298" t="n">
-        <v>25819</v>
+        <v>35090</v>
       </c>
       <c r="C298" t="n">
-        <v>115.89</v>
+        <v>109.98</v>
       </c>
       <c r="D298" t="n">
-        <v>18004</v>
+        <v>14268</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>94.3</v>
+        <v>106.23</v>
       </c>
       <c r="B299" t="n">
-        <v>31710</v>
+        <v>34831</v>
       </c>
       <c r="C299" t="n">
-        <v>91.98</v>
+        <v>79.53</v>
       </c>
       <c r="D299" t="n">
-        <v>21718</v>
+        <v>26895</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>89.70999999999999</v>
+        <v>106.57</v>
       </c>
       <c r="B300" t="n">
-        <v>21155</v>
+        <v>33946</v>
       </c>
       <c r="C300" t="n">
-        <v>86.37</v>
+        <v>116.04</v>
       </c>
       <c r="D300" t="n">
-        <v>19633</v>
+        <v>22310</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>97.97</v>
+        <v>106.7</v>
       </c>
       <c r="B301" t="n">
-        <v>41522</v>
+        <v>33827</v>
       </c>
       <c r="C301" t="n">
-        <v>97.53</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="D301" t="n">
-        <v>28602</v>
+        <v>22432</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>101.58</v>
+        <v>106.87</v>
       </c>
       <c r="B302" t="n">
-        <v>45077</v>
+        <v>33000</v>
       </c>
       <c r="C302" t="n">
-        <v>99.88</v>
+        <v>106.48</v>
       </c>
       <c r="D302" t="n">
-        <v>11936</v>
+        <v>26901</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>108.72</v>
+        <v>107.56</v>
       </c>
       <c r="B303" t="n">
-        <v>37488</v>
+        <v>31411</v>
       </c>
       <c r="C303" t="n">
-        <v>105.33</v>
+        <v>105.82</v>
       </c>
       <c r="D303" t="n">
-        <v>27459</v>
+        <v>20104</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>91.43000000000001</v>
+        <v>107.92</v>
       </c>
       <c r="B304" t="n">
-        <v>25122</v>
+        <v>30677</v>
       </c>
       <c r="C304" t="n">
-        <v>91.14</v>
+        <v>93.69</v>
       </c>
       <c r="D304" t="n">
-        <v>12066</v>
+        <v>29769</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>163.48</v>
+        <v>108.08</v>
       </c>
       <c r="B305" t="n">
-        <v>24409</v>
+        <v>31972</v>
       </c>
       <c r="C305" t="n">
-        <v>158.07</v>
+        <v>105.41</v>
       </c>
       <c r="D305" t="n">
-        <v>25019</v>
+        <v>20961</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>97.23</v>
+        <v>108.48</v>
       </c>
       <c r="B306" t="n">
-        <v>41112</v>
+        <v>29266</v>
       </c>
       <c r="C306" t="n">
-        <v>97.54000000000001</v>
+        <v>122.33</v>
       </c>
       <c r="D306" t="n">
-        <v>15351</v>
+        <v>26573</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>96.38</v>
+        <v>108.7</v>
       </c>
       <c r="B307" t="n">
-        <v>37608</v>
+        <v>30468</v>
       </c>
       <c r="C307" t="n">
-        <v>98.75</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="D307" t="n">
-        <v>23071</v>
+        <v>29134</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>92.41</v>
+        <v>108.71</v>
       </c>
       <c r="B308" t="n">
-        <v>29259</v>
+        <v>29970</v>
       </c>
       <c r="C308" t="n">
-        <v>92.34999999999999</v>
+        <v>114.26</v>
       </c>
       <c r="D308" t="n">
-        <v>21435</v>
+        <v>17941</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>111.07</v>
+        <v>108.78</v>
       </c>
       <c r="B309" t="n">
-        <v>31464</v>
+        <v>32073</v>
       </c>
       <c r="C309" t="n">
-        <v>109.35</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="D309" t="n">
-        <v>19086</v>
+        <v>28598</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>9.109999999999999</v>
+        <v>108.99</v>
       </c>
       <c r="B310" t="n">
-        <v>24937</v>
+        <v>29120</v>
       </c>
       <c r="C310" t="n">
-        <v>8.390000000000001</v>
+        <v>117.35</v>
       </c>
       <c r="D310" t="n">
-        <v>20110</v>
+        <v>16083</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>35.48</v>
+        <v>109.31</v>
       </c>
       <c r="B311" t="n">
-        <v>22865</v>
+        <v>27800</v>
       </c>
       <c r="C311" t="n">
-        <v>35.93</v>
+        <v>103.21</v>
       </c>
       <c r="D311" t="n">
-        <v>12764</v>
+        <v>19327</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>25.82</v>
+        <v>109.78</v>
       </c>
       <c r="B312" t="n">
-        <v>23443</v>
+        <v>25904</v>
       </c>
       <c r="C312" t="n">
-        <v>26.32</v>
+        <v>118.1</v>
       </c>
       <c r="D312" t="n">
-        <v>23183</v>
+        <v>16805</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>91.81</v>
+        <v>110.84</v>
       </c>
       <c r="B313" t="n">
-        <v>26579</v>
+        <v>25763</v>
       </c>
       <c r="C313" t="n">
-        <v>89.06999999999999</v>
+        <v>116.9</v>
       </c>
       <c r="D313" t="n">
-        <v>15800</v>
+        <v>29061</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>93.59999999999999</v>
+        <v>111.06</v>
       </c>
       <c r="B314" t="n">
-        <v>27214</v>
+        <v>26083</v>
       </c>
       <c r="C314" t="n">
-        <v>95.73999999999999</v>
+        <v>119.74</v>
       </c>
       <c r="D314" t="n">
-        <v>16629</v>
+        <v>19029</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>110.36</v>
+        <v>111.08</v>
       </c>
       <c r="B315" t="n">
-        <v>28916</v>
+        <v>24285</v>
       </c>
       <c r="C315" t="n">
-        <v>109.11</v>
+        <v>120.91</v>
       </c>
       <c r="D315" t="n">
-        <v>18254</v>
+        <v>16634</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>104.57</v>
+        <v>111.15</v>
       </c>
       <c r="B316" t="n">
-        <v>45767</v>
+        <v>25607</v>
       </c>
       <c r="C316" t="n">
-        <v>108.31</v>
+        <v>110.19</v>
       </c>
       <c r="D316" t="n">
-        <v>27313</v>
+        <v>12982</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>93.54000000000001</v>
+        <v>111.46</v>
       </c>
       <c r="B317" t="n">
-        <v>29903</v>
+        <v>23971</v>
       </c>
       <c r="C317" t="n">
-        <v>94.59999999999999</v>
+        <v>114.41</v>
       </c>
       <c r="D317" t="n">
-        <v>29849</v>
+        <v>25458</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>94.15000000000001</v>
+        <v>111.91</v>
       </c>
       <c r="B318" t="n">
-        <v>29432</v>
+        <v>22486</v>
       </c>
       <c r="C318" t="n">
-        <v>94.20999999999999</v>
+        <v>103.15</v>
       </c>
       <c r="D318" t="n">
-        <v>23363</v>
+        <v>22141</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>110.09</v>
+        <v>113.58</v>
       </c>
       <c r="B319" t="n">
-        <v>34270</v>
+        <v>21663</v>
       </c>
       <c r="C319" t="n">
-        <v>108.78</v>
+        <v>99.91</v>
       </c>
       <c r="D319" t="n">
-        <v>17995</v>
+        <v>17894</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>98.31</v>
+        <v>114.57</v>
       </c>
       <c r="B320" t="n">
-        <v>41727</v>
+        <v>20964</v>
       </c>
       <c r="C320" t="n">
-        <v>100.93</v>
+        <v>139.29</v>
       </c>
       <c r="D320" t="n">
-        <v>27343</v>
+        <v>19088</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>92.59</v>
+        <v>115.17</v>
       </c>
       <c r="B321" t="n">
-        <v>29531</v>
+        <v>20945</v>
       </c>
       <c r="C321" t="n">
-        <v>92.20999999999999</v>
+        <v>117.67</v>
       </c>
       <c r="D321" t="n">
-        <v>27380</v>
+        <v>26433</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>154.7</v>
+        <v>115.56</v>
       </c>
       <c r="B322" t="n">
-        <v>23060</v>
+        <v>19656</v>
       </c>
       <c r="C322" t="n">
-        <v>153.36</v>
+        <v>103.84</v>
       </c>
       <c r="D322" t="n">
-        <v>11334</v>
+        <v>18685</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>13.3</v>
+        <v>116.09</v>
       </c>
       <c r="B323" t="n">
-        <v>23703</v>
+        <v>19070</v>
       </c>
       <c r="C323" t="n">
-        <v>12.21</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D323" t="n">
-        <v>27835</v>
+        <v>26879</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>104.86</v>
+        <v>116.47</v>
       </c>
       <c r="B324" t="n">
-        <v>47298</v>
+        <v>21559</v>
       </c>
       <c r="C324" t="n">
-        <v>106.31</v>
+        <v>122.83</v>
       </c>
       <c r="D324" t="n">
-        <v>17367</v>
+        <v>19900</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>104.07</v>
+        <v>117.58</v>
       </c>
       <c r="B325" t="n">
-        <v>48537</v>
+        <v>19425</v>
       </c>
       <c r="C325" t="n">
-        <v>107.8</v>
+        <v>125.76</v>
       </c>
       <c r="D325" t="n">
-        <v>27219</v>
+        <v>25926</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>107.27</v>
+        <v>117.89</v>
       </c>
       <c r="B326" t="n">
-        <v>38487</v>
+        <v>21242</v>
       </c>
       <c r="C326" t="n">
-        <v>105.68</v>
+        <v>126.1</v>
       </c>
       <c r="D326" t="n">
-        <v>10532</v>
+        <v>16733</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>94.20999999999999</v>
+        <v>118.01</v>
       </c>
       <c r="B327" t="n">
-        <v>33332</v>
+        <v>18692</v>
       </c>
       <c r="C327" t="n">
-        <v>91.78</v>
+        <v>132.88</v>
       </c>
       <c r="D327" t="n">
-        <v>11068</v>
+        <v>15015</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>98.26000000000001</v>
+        <v>118.36</v>
       </c>
       <c r="B328" t="n">
-        <v>43507</v>
+        <v>19563</v>
       </c>
       <c r="C328" t="n">
-        <v>99.89</v>
+        <v>107.2</v>
       </c>
       <c r="D328" t="n">
-        <v>12108</v>
+        <v>20513</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>109.54</v>
+        <v>118.45</v>
       </c>
       <c r="B329" t="n">
-        <v>33681</v>
+        <v>21363</v>
       </c>
       <c r="C329" t="n">
-        <v>108.66</v>
+        <v>118.13</v>
       </c>
       <c r="D329" t="n">
-        <v>14034</v>
+        <v>10063</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>8.4</v>
+        <v>118.6</v>
       </c>
       <c r="B330" t="n">
-        <v>20868</v>
+        <v>18689</v>
       </c>
       <c r="C330" t="n">
-        <v>8.19</v>
+        <v>108.66</v>
       </c>
       <c r="D330" t="n">
-        <v>29132</v>
+        <v>19586</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>114.98</v>
+        <v>118.81</v>
       </c>
       <c r="B331" t="n">
-        <v>21508</v>
+        <v>18239</v>
       </c>
       <c r="C331" t="n">
-        <v>118.27</v>
+        <v>123.77</v>
       </c>
       <c r="D331" t="n">
-        <v>23797</v>
+        <v>29847</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>153.39</v>
+        <v>119.02</v>
       </c>
       <c r="B332" t="n">
-        <v>22047</v>
+        <v>17757</v>
       </c>
       <c r="C332" t="n">
-        <v>154.37</v>
+        <v>100.75</v>
       </c>
       <c r="D332" t="n">
-        <v>19904</v>
+        <v>28985</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>52.85</v>
+        <v>119.07</v>
       </c>
       <c r="B333" t="n">
-        <v>21186</v>
+        <v>19074</v>
       </c>
       <c r="C333" t="n">
-        <v>54.54</v>
+        <v>108.87</v>
       </c>
       <c r="D333" t="n">
-        <v>24893</v>
+        <v>12315</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>111.61</v>
+        <v>119.75</v>
       </c>
       <c r="B334" t="n">
-        <v>28608</v>
+        <v>17590</v>
       </c>
       <c r="C334" t="n">
-        <v>114.39</v>
+        <v>143.79</v>
       </c>
       <c r="D334" t="n">
-        <v>10798</v>
+        <v>10365</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>59.64</v>
+        <v>120.05</v>
       </c>
       <c r="B335" t="n">
-        <v>21484</v>
+        <v>18788</v>
       </c>
       <c r="C335" t="n">
-        <v>61.33</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="D335" t="n">
-        <v>26844</v>
+        <v>11609</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>114.97</v>
+        <v>120.08</v>
       </c>
       <c r="B336" t="n">
-        <v>23084</v>
+        <v>19547</v>
       </c>
       <c r="C336" t="n">
-        <v>117.97</v>
+        <v>138.12</v>
       </c>
       <c r="D336" t="n">
-        <v>17848</v>
+        <v>15570</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>114</v>
+        <v>120.74</v>
       </c>
       <c r="B337" t="n">
-        <v>22709</v>
+        <v>20170</v>
       </c>
       <c r="C337" t="n">
-        <v>115.23</v>
+        <v>103.71</v>
       </c>
       <c r="D337" t="n">
-        <v>16915</v>
+        <v>14306</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>98.33</v>
+        <v>121.4</v>
       </c>
       <c r="B338" t="n">
-        <v>41622</v>
+        <v>19972</v>
       </c>
       <c r="C338" t="n">
-        <v>101.91</v>
+        <v>141.31</v>
       </c>
       <c r="D338" t="n">
-        <v>26224</v>
+        <v>18516</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>105.99</v>
+        <v>121.51</v>
       </c>
       <c r="B339" t="n">
-        <v>41904</v>
+        <v>21494</v>
       </c>
       <c r="C339" t="n">
-        <v>107.9</v>
+        <v>132.42</v>
       </c>
       <c r="D339" t="n">
-        <v>28917</v>
+        <v>14287</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>92.84999999999999</v>
+        <v>122.27</v>
       </c>
       <c r="B340" t="n">
-        <v>26729</v>
+        <v>19314</v>
       </c>
       <c r="C340" t="n">
-        <v>95.83</v>
+        <v>142.24</v>
       </c>
       <c r="D340" t="n">
-        <v>12622</v>
+        <v>23470</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>108.91</v>
+        <v>122.41</v>
       </c>
       <c r="B341" t="n">
-        <v>35012</v>
+        <v>19202</v>
       </c>
       <c r="C341" t="n">
-        <v>108.58</v>
+        <v>108.22</v>
       </c>
       <c r="D341" t="n">
-        <v>16806</v>
+        <v>16743</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>129.36</v>
+        <v>122.99</v>
       </c>
       <c r="B342" t="n">
-        <v>25818</v>
+        <v>20823</v>
       </c>
       <c r="C342" t="n">
-        <v>124.54</v>
+        <v>129.72</v>
       </c>
       <c r="D342" t="n">
-        <v>24851</v>
+        <v>20636</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>95.22</v>
+        <v>123.73</v>
       </c>
       <c r="B343" t="n">
-        <v>36590</v>
+        <v>18429</v>
       </c>
       <c r="C343" t="n">
-        <v>96.33</v>
+        <v>102.51</v>
       </c>
       <c r="D343" t="n">
-        <v>14842</v>
+        <v>21052</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>101.99</v>
+        <v>124.17</v>
       </c>
       <c r="B344" t="n">
-        <v>45045</v>
+        <v>18330</v>
       </c>
       <c r="C344" t="n">
-        <v>97.62</v>
+        <v>127.1</v>
       </c>
       <c r="D344" t="n">
-        <v>18525</v>
+        <v>23009</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>108.71</v>
+        <v>124.44</v>
       </c>
       <c r="B345" t="n">
-        <v>36666</v>
+        <v>20038</v>
       </c>
       <c r="C345" t="n">
-        <v>112.66</v>
+        <v>102.26</v>
       </c>
       <c r="D345" t="n">
-        <v>13160</v>
+        <v>13979</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>108.3</v>
+        <v>125.2</v>
       </c>
       <c r="B346" t="n">
-        <v>38607</v>
+        <v>19530</v>
       </c>
       <c r="C346" t="n">
-        <v>109.73</v>
+        <v>103.26</v>
       </c>
       <c r="D346" t="n">
-        <v>17791</v>
+        <v>27281</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>92.59</v>
+        <v>125.52</v>
       </c>
       <c r="B347" t="n">
-        <v>29038</v>
+        <v>19613</v>
       </c>
       <c r="C347" t="n">
-        <v>91.04000000000001</v>
+        <v>118.74</v>
       </c>
       <c r="D347" t="n">
-        <v>24553</v>
+        <v>20503</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>94.81</v>
+        <v>125.72</v>
       </c>
       <c r="B348" t="n">
-        <v>31460</v>
+        <v>21033</v>
       </c>
       <c r="C348" t="n">
-        <v>91.41</v>
+        <v>96.09</v>
       </c>
       <c r="D348" t="n">
-        <v>27342</v>
+        <v>19283</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>95.31999999999999</v>
+        <v>126.15</v>
       </c>
       <c r="B349" t="n">
-        <v>35855</v>
+        <v>20055</v>
       </c>
       <c r="C349" t="n">
-        <v>97.56999999999999</v>
+        <v>127.88</v>
       </c>
       <c r="D349" t="n">
-        <v>23758</v>
+        <v>13406</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>96.88</v>
+        <v>126.36</v>
       </c>
       <c r="B350" t="n">
-        <v>40583</v>
+        <v>19510</v>
       </c>
       <c r="C350" t="n">
-        <v>98.66</v>
+        <v>157.02</v>
       </c>
       <c r="D350" t="n">
-        <v>16195</v>
+        <v>20827</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>90.93000000000001</v>
+        <v>126.6</v>
       </c>
       <c r="B351" t="n">
-        <v>24886</v>
+        <v>19047</v>
       </c>
       <c r="C351" t="n">
-        <v>90.14</v>
+        <v>120.54</v>
       </c>
       <c r="D351" t="n">
-        <v>27172</v>
+        <v>24853</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>101.54</v>
+        <v>126.94</v>
       </c>
       <c r="B352" t="n">
-        <v>47941</v>
+        <v>20043</v>
       </c>
       <c r="C352" t="n">
-        <v>103.12</v>
+        <v>151.14</v>
       </c>
       <c r="D352" t="n">
-        <v>21120</v>
+        <v>11300</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>108.88</v>
+        <v>127.12</v>
       </c>
       <c r="B353" t="n">
-        <v>35269</v>
+        <v>19156</v>
       </c>
       <c r="C353" t="n">
-        <v>108.11</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="D353" t="n">
-        <v>28767</v>
+        <v>17323</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>102.98</v>
+        <v>127.43</v>
       </c>
       <c r="B354" t="n">
-        <v>47864</v>
+        <v>19599</v>
       </c>
       <c r="C354" t="n">
-        <v>102.72</v>
+        <v>116.5</v>
       </c>
       <c r="D354" t="n">
-        <v>22789</v>
+        <v>25121</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>68.03</v>
+        <v>127.45</v>
       </c>
       <c r="B355" t="n">
-        <v>24628</v>
+        <v>18788</v>
       </c>
       <c r="C355" t="n">
-        <v>69.93000000000001</v>
+        <v>126.44</v>
       </c>
       <c r="D355" t="n">
-        <v>19233</v>
+        <v>26590</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>147.18</v>
+        <v>127.5</v>
       </c>
       <c r="B356" t="n">
-        <v>20773</v>
+        <v>18658</v>
       </c>
       <c r="C356" t="n">
-        <v>145.95</v>
+        <v>106.7</v>
       </c>
       <c r="D356" t="n">
-        <v>16389</v>
+        <v>15076</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>95.76000000000001</v>
+        <v>127.93</v>
       </c>
       <c r="B357" t="n">
-        <v>35554</v>
+        <v>21084</v>
       </c>
       <c r="C357" t="n">
-        <v>92.92</v>
+        <v>138.9</v>
       </c>
       <c r="D357" t="n">
-        <v>26104</v>
+        <v>14696</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>109.58</v>
+        <v>128.03</v>
       </c>
       <c r="B358" t="n">
-        <v>33979</v>
+        <v>19717</v>
       </c>
       <c r="C358" t="n">
-        <v>105.84</v>
+        <v>130.92</v>
       </c>
       <c r="D358" t="n">
-        <v>28585</v>
+        <v>29924</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>114.75</v>
+        <v>128.36</v>
       </c>
       <c r="B359" t="n">
-        <v>22524</v>
+        <v>16714</v>
       </c>
       <c r="C359" t="n">
-        <v>116.19</v>
+        <v>133.19</v>
       </c>
       <c r="D359" t="n">
-        <v>13803</v>
+        <v>20786</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>95.06</v>
+        <v>128.8</v>
       </c>
       <c r="B360" t="n">
-        <v>35385</v>
+        <v>18355</v>
       </c>
       <c r="C360" t="n">
-        <v>96.78</v>
+        <v>149.01</v>
       </c>
       <c r="D360" t="n">
-        <v>16951</v>
+        <v>17132</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>93.48</v>
+        <v>128.93</v>
       </c>
       <c r="B361" t="n">
-        <v>26941</v>
+        <v>18429</v>
       </c>
       <c r="C361" t="n">
-        <v>96.73</v>
+        <v>123.78</v>
       </c>
       <c r="D361" t="n">
-        <v>13323</v>
+        <v>10625</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>94.23</v>
+        <v>128.94</v>
       </c>
       <c r="B362" t="n">
-        <v>30888</v>
+        <v>20456</v>
       </c>
       <c r="C362" t="n">
-        <v>92.34</v>
+        <v>155</v>
       </c>
       <c r="D362" t="n">
-        <v>25997</v>
+        <v>23566</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>106.56</v>
+        <v>129.04</v>
       </c>
       <c r="B363" t="n">
-        <v>41142</v>
+        <v>22032</v>
       </c>
       <c r="C363" t="n">
-        <v>109.3</v>
+        <v>106.11</v>
       </c>
       <c r="D363" t="n">
-        <v>18096</v>
+        <v>17684</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>56.94</v>
+        <v>129.25</v>
       </c>
       <c r="B364" t="n">
-        <v>22929</v>
+        <v>18635</v>
       </c>
       <c r="C364" t="n">
-        <v>58.57</v>
+        <v>152.25</v>
       </c>
       <c r="D364" t="n">
-        <v>15345</v>
+        <v>11661</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>111.95</v>
+        <v>130.28</v>
       </c>
       <c r="B365" t="n">
-        <v>26395</v>
+        <v>18565</v>
       </c>
       <c r="C365" t="n">
-        <v>111.01</v>
+        <v>126.69</v>
       </c>
       <c r="D365" t="n">
-        <v>25490</v>
+        <v>12220</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>109.52</v>
+        <v>130.99</v>
       </c>
       <c r="B366" t="n">
-        <v>36487</v>
+        <v>20810</v>
       </c>
       <c r="C366" t="n">
-        <v>108.6</v>
+        <v>122.27</v>
       </c>
       <c r="D366" t="n">
-        <v>24944</v>
+        <v>23841</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>90.08</v>
+        <v>131.27</v>
       </c>
       <c r="B367" t="n">
-        <v>20535</v>
+        <v>18162</v>
       </c>
       <c r="C367" t="n">
-        <v>90.29000000000001</v>
+        <v>104.37</v>
       </c>
       <c r="D367" t="n">
-        <v>21766</v>
+        <v>17389</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>114.81</v>
+        <v>131.63</v>
       </c>
       <c r="B368" t="n">
-        <v>21231</v>
+        <v>19949</v>
       </c>
       <c r="C368" t="n">
-        <v>117.5</v>
+        <v>167.07</v>
       </c>
       <c r="D368" t="n">
-        <v>20865</v>
+        <v>17012</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>94.63</v>
+        <v>131.69</v>
       </c>
       <c r="B369" t="n">
-        <v>33604</v>
+        <v>19466</v>
       </c>
       <c r="C369" t="n">
-        <v>92.45999999999999</v>
+        <v>134.41</v>
       </c>
       <c r="D369" t="n">
-        <v>22391</v>
+        <v>22676</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>100.24</v>
+        <v>132.52</v>
       </c>
       <c r="B370" t="n">
-        <v>44131</v>
+        <v>17985</v>
       </c>
       <c r="C370" t="n">
-        <v>96.93000000000001</v>
+        <v>154.63</v>
       </c>
       <c r="D370" t="n">
-        <v>26932</v>
+        <v>13075</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>108.46</v>
+        <v>132.6</v>
       </c>
       <c r="B371" t="n">
-        <v>36529</v>
+        <v>18188</v>
       </c>
       <c r="C371" t="n">
-        <v>108.14</v>
+        <v>143.29</v>
       </c>
       <c r="D371" t="n">
-        <v>24808</v>
+        <v>20329</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>103.11</v>
+        <v>132.94</v>
       </c>
       <c r="B372" t="n">
-        <v>47259</v>
+        <v>21556</v>
       </c>
       <c r="C372" t="n">
-        <v>99.17</v>
+        <v>136.13</v>
       </c>
       <c r="D372" t="n">
-        <v>16478</v>
+        <v>21303</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>103.52</v>
+        <v>133.39</v>
       </c>
       <c r="B373" t="n">
-        <v>47226</v>
+        <v>19031</v>
       </c>
       <c r="C373" t="n">
-        <v>105.64</v>
+        <v>131.41</v>
       </c>
       <c r="D373" t="n">
-        <v>12139</v>
+        <v>14532</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>104.63</v>
+        <v>133.51</v>
       </c>
       <c r="B374" t="n">
-        <v>47785</v>
+        <v>18775</v>
       </c>
       <c r="C374" t="n">
-        <v>109.31</v>
+        <v>144.51</v>
       </c>
       <c r="D374" t="n">
-        <v>20796</v>
+        <v>19570</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>92.23999999999999</v>
+        <v>133.79</v>
       </c>
       <c r="B375" t="n">
-        <v>29709</v>
+        <v>19091</v>
       </c>
       <c r="C375" t="n">
-        <v>93.72</v>
+        <v>119.05</v>
       </c>
       <c r="D375" t="n">
-        <v>13266</v>
+        <v>28202</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>45.77</v>
+        <v>134.64</v>
       </c>
       <c r="B376" t="n">
-        <v>26079</v>
+        <v>20723</v>
       </c>
       <c r="C376" t="n">
-        <v>44.96</v>
+        <v>104.51</v>
       </c>
       <c r="D376" t="n">
-        <v>15856</v>
+        <v>11475</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>110.37</v>
+        <v>135.17</v>
       </c>
       <c r="B377" t="n">
-        <v>32108</v>
+        <v>20404</v>
       </c>
       <c r="C377" t="n">
-        <v>114.23</v>
+        <v>156.64</v>
       </c>
       <c r="D377" t="n">
-        <v>24678</v>
+        <v>18209</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>100.95</v>
+        <v>135.8</v>
       </c>
       <c r="B378" t="n">
-        <v>45308</v>
+        <v>20105</v>
       </c>
       <c r="C378" t="n">
-        <v>98.23</v>
+        <v>163.52</v>
       </c>
       <c r="D378" t="n">
-        <v>25743</v>
+        <v>15204</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>178.27</v>
+        <v>136.62</v>
       </c>
       <c r="B379" t="n">
-        <v>22457</v>
+        <v>17747</v>
       </c>
       <c r="C379" t="n">
-        <v>180</v>
+        <v>143.69</v>
       </c>
       <c r="D379" t="n">
-        <v>10387</v>
+        <v>25180</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>110.11</v>
+        <v>138.45</v>
       </c>
       <c r="B380" t="n">
-        <v>30465</v>
+        <v>20067</v>
       </c>
       <c r="C380" t="n">
-        <v>110.91</v>
+        <v>170.18</v>
       </c>
       <c r="D380" t="n">
-        <v>12942</v>
+        <v>14154</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>112.95</v>
+        <v>138.62</v>
       </c>
       <c r="B381" t="n">
-        <v>23574</v>
+        <v>17899</v>
       </c>
       <c r="C381" t="n">
-        <v>116.2</v>
+        <v>142.55</v>
       </c>
       <c r="D381" t="n">
-        <v>16647</v>
+        <v>25268</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>97.34</v>
+        <v>138.78</v>
       </c>
       <c r="B382" t="n">
-        <v>37809</v>
+        <v>16606</v>
       </c>
       <c r="C382" t="n">
-        <v>94.34</v>
+        <v>149.04</v>
       </c>
       <c r="D382" t="n">
-        <v>16410</v>
+        <v>16164</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>19.68</v>
+        <v>138.86</v>
       </c>
       <c r="B383" t="n">
-        <v>25821</v>
+        <v>19683</v>
       </c>
       <c r="C383" t="n">
-        <v>20.61</v>
+        <v>123.68</v>
       </c>
       <c r="D383" t="n">
-        <v>16712</v>
+        <v>23204</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>106.23</v>
+        <v>139.02</v>
       </c>
       <c r="B384" t="n">
-        <v>45964</v>
+        <v>19224</v>
       </c>
       <c r="C384" t="n">
-        <v>108.49</v>
+        <v>159.38</v>
       </c>
       <c r="D384" t="n">
-        <v>11203</v>
+        <v>19706</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>42.53</v>
+        <v>139.27</v>
       </c>
       <c r="B385" t="n">
-        <v>24226</v>
+        <v>16529</v>
       </c>
       <c r="C385" t="n">
-        <v>42.22</v>
+        <v>140.17</v>
       </c>
       <c r="D385" t="n">
-        <v>29529</v>
+        <v>29494</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>104.37</v>
+        <v>139.39</v>
       </c>
       <c r="B386" t="n">
-        <v>44508</v>
+        <v>19533</v>
       </c>
       <c r="C386" t="n">
-        <v>103.97</v>
+        <v>152.69</v>
       </c>
       <c r="D386" t="n">
-        <v>25739</v>
+        <v>14592</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>109.15</v>
+        <v>139.45</v>
       </c>
       <c r="B387" t="n">
-        <v>32587</v>
+        <v>19630</v>
       </c>
       <c r="C387" t="n">
-        <v>109.83</v>
+        <v>153.66</v>
       </c>
       <c r="D387" t="n">
-        <v>14867</v>
+        <v>19102</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>106.59</v>
+        <v>139.5</v>
       </c>
       <c r="B388" t="n">
-        <v>44648</v>
+        <v>19487</v>
       </c>
       <c r="C388" t="n">
-        <v>109.53</v>
+        <v>129.49</v>
       </c>
       <c r="D388" t="n">
-        <v>18893</v>
+        <v>11422</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>98.43000000000001</v>
+        <v>140.53</v>
       </c>
       <c r="B389" t="n">
-        <v>38755</v>
+        <v>20289</v>
       </c>
       <c r="C389" t="n">
-        <v>100.97</v>
+        <v>137.25</v>
       </c>
       <c r="D389" t="n">
-        <v>23020</v>
+        <v>29497</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>106.16</v>
+        <v>140.59</v>
       </c>
       <c r="B390" t="n">
-        <v>43875</v>
+        <v>20582</v>
       </c>
       <c r="C390" t="n">
-        <v>106.29</v>
+        <v>129.49</v>
       </c>
       <c r="D390" t="n">
-        <v>15289</v>
+        <v>10080</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>63.86</v>
+        <v>140.59</v>
       </c>
       <c r="B391" t="n">
-        <v>24395</v>
+        <v>18566</v>
       </c>
       <c r="C391" t="n">
-        <v>61.97</v>
+        <v>148.25</v>
       </c>
       <c r="D391" t="n">
-        <v>25408</v>
+        <v>24129</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>96.62</v>
+        <v>140.91</v>
       </c>
       <c r="B392" t="n">
-        <v>38753</v>
+        <v>19011</v>
       </c>
       <c r="C392" t="n">
-        <v>93.77</v>
+        <v>129.68</v>
       </c>
       <c r="D392" t="n">
-        <v>29331</v>
+        <v>26306</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>10.42</v>
+        <v>140.99</v>
       </c>
       <c r="B393" t="n">
-        <v>23886</v>
+        <v>19482</v>
       </c>
       <c r="C393" t="n">
-        <v>10.17</v>
+        <v>132.39</v>
       </c>
       <c r="D393" t="n">
-        <v>20129</v>
+        <v>19521</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>112.66</v>
+        <v>141.17</v>
       </c>
       <c r="B394" t="n">
-        <v>24381</v>
+        <v>19291</v>
       </c>
       <c r="C394" t="n">
-        <v>115.22</v>
+        <v>155.06</v>
       </c>
       <c r="D394" t="n">
-        <v>14027</v>
+        <v>25198</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>113.74</v>
+        <v>141.46</v>
       </c>
       <c r="B395" t="n">
-        <v>24844</v>
+        <v>20201</v>
       </c>
       <c r="C395" t="n">
-        <v>109.07</v>
+        <v>139.04</v>
       </c>
       <c r="D395" t="n">
-        <v>22510</v>
+        <v>23529</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>90.28</v>
+        <v>141.59</v>
       </c>
       <c r="B396" t="n">
-        <v>20526</v>
+        <v>16733</v>
       </c>
       <c r="C396" t="n">
-        <v>94.15000000000001</v>
+        <v>115.8</v>
       </c>
       <c r="D396" t="n">
-        <v>13057</v>
+        <v>16697</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>106.67</v>
+        <v>141.83</v>
       </c>
       <c r="B397" t="n">
-        <v>41882</v>
+        <v>18883</v>
       </c>
       <c r="C397" t="n">
-        <v>104.59</v>
+        <v>119.93</v>
       </c>
       <c r="D397" t="n">
-        <v>29491</v>
+        <v>28535</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>94.97</v>
+        <v>142.23</v>
       </c>
       <c r="B398" t="n">
-        <v>33302</v>
+        <v>17647</v>
       </c>
       <c r="C398" t="n">
-        <v>93.7</v>
+        <v>117.58</v>
       </c>
       <c r="D398" t="n">
-        <v>21197</v>
+        <v>10049</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>99.66</v>
+        <v>142.96</v>
       </c>
       <c r="B399" t="n">
-        <v>43291</v>
+        <v>18955</v>
       </c>
       <c r="C399" t="n">
-        <v>97.44</v>
+        <v>120.52</v>
       </c>
       <c r="D399" t="n">
-        <v>16055</v>
+        <v>15528</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>23.57</v>
+        <v>143.09</v>
       </c>
       <c r="B400" t="n">
-        <v>23175</v>
+        <v>18598</v>
       </c>
       <c r="C400" t="n">
-        <v>23.79</v>
+        <v>152.71</v>
       </c>
       <c r="D400" t="n">
-        <v>19581</v>
+        <v>17021</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>18.6</v>
+        <v>143.29</v>
       </c>
       <c r="B401" t="n">
-        <v>23812</v>
+        <v>18959</v>
       </c>
       <c r="C401" t="n">
-        <v>18.53</v>
+        <v>145.73</v>
       </c>
       <c r="D401" t="n">
-        <v>25074</v>
+        <v>22497</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>108.9</v>
+        <v>143.79</v>
       </c>
       <c r="B402" t="n">
-        <v>34788</v>
+        <v>18643</v>
       </c>
       <c r="C402" t="n">
-        <v>106.49</v>
+        <v>142.24</v>
       </c>
       <c r="D402" t="n">
-        <v>10445</v>
+        <v>23351</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>163.33</v>
+        <v>144.42</v>
       </c>
       <c r="B403" t="n">
-        <v>19162</v>
+        <v>20422</v>
       </c>
       <c r="C403" t="n">
-        <v>161.65</v>
+        <v>123.29</v>
       </c>
       <c r="D403" t="n">
-        <v>21776</v>
+        <v>10428</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>110.22</v>
+        <v>144.59</v>
       </c>
       <c r="B404" t="n">
-        <v>32009</v>
+        <v>23769</v>
       </c>
       <c r="C404" t="n">
-        <v>107.59</v>
+        <v>124.91</v>
       </c>
       <c r="D404" t="n">
-        <v>26994</v>
+        <v>21780</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>106.29</v>
+        <v>144.63</v>
       </c>
       <c r="B405" t="n">
-        <v>41377</v>
+        <v>21482</v>
       </c>
       <c r="C405" t="n">
-        <v>102.73</v>
+        <v>151.98</v>
       </c>
       <c r="D405" t="n">
-        <v>25877</v>
+        <v>19333</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>105.26</v>
+        <v>144.71</v>
       </c>
       <c r="B406" t="n">
-        <v>43966</v>
+        <v>21053</v>
       </c>
       <c r="C406" t="n">
-        <v>105.89</v>
+        <v>171.09</v>
       </c>
       <c r="D406" t="n">
-        <v>27890</v>
+        <v>12951</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>93.37</v>
+        <v>144.81</v>
       </c>
       <c r="B407" t="n">
-        <v>31130</v>
+        <v>21384</v>
       </c>
       <c r="C407" t="n">
-        <v>93.53</v>
+        <v>139.09</v>
       </c>
       <c r="D407" t="n">
-        <v>20051</v>
+        <v>11224</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>93.77</v>
+        <v>145.15</v>
       </c>
       <c r="B408" t="n">
-        <v>30363</v>
+        <v>19833</v>
       </c>
       <c r="C408" t="n">
-        <v>96.89</v>
+        <v>159.13</v>
       </c>
       <c r="D408" t="n">
-        <v>15419</v>
+        <v>23530</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>95.89</v>
+        <v>145.47</v>
       </c>
       <c r="B409" t="n">
-        <v>36450</v>
+        <v>18604</v>
       </c>
       <c r="C409" t="n">
-        <v>91.63</v>
+        <v>168.49</v>
       </c>
       <c r="D409" t="n">
-        <v>22275</v>
+        <v>23498</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>98.2</v>
+        <v>146.03</v>
       </c>
       <c r="B410" t="n">
-        <v>42246</v>
+        <v>21079</v>
       </c>
       <c r="C410" t="n">
-        <v>97.97</v>
+        <v>152.95</v>
       </c>
       <c r="D410" t="n">
-        <v>24803</v>
+        <v>16669</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>108.44</v>
+        <v>146.2</v>
       </c>
       <c r="B411" t="n">
-        <v>35181</v>
+        <v>23060</v>
       </c>
       <c r="C411" t="n">
-        <v>107.31</v>
+        <v>146.89</v>
       </c>
       <c r="D411" t="n">
-        <v>28053</v>
+        <v>23139</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>170.49</v>
+        <v>146.33</v>
       </c>
       <c r="B412" t="n">
-        <v>21012</v>
+        <v>23871</v>
       </c>
       <c r="C412" t="n">
-        <v>176.83</v>
+        <v>153.03</v>
       </c>
       <c r="D412" t="n">
-        <v>17020</v>
+        <v>20504</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>108.76</v>
+        <v>146.52</v>
       </c>
       <c r="B413" t="n">
-        <v>36811</v>
+        <v>19679</v>
       </c>
       <c r="C413" t="n">
-        <v>106.7</v>
+        <v>172.51</v>
       </c>
       <c r="D413" t="n">
-        <v>14707</v>
+        <v>28694</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>106.11</v>
+        <v>146.68</v>
       </c>
       <c r="B414" t="n">
-        <v>43258</v>
+        <v>20265</v>
       </c>
       <c r="C414" t="n">
-        <v>101.98</v>
+        <v>123.3</v>
       </c>
       <c r="D414" t="n">
-        <v>11305</v>
+        <v>11158</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>100.99</v>
+        <v>147.5</v>
       </c>
       <c r="B415" t="n">
-        <v>47728</v>
+        <v>23873</v>
       </c>
       <c r="C415" t="n">
-        <v>98.54000000000001</v>
+        <v>159.61</v>
       </c>
       <c r="D415" t="n">
-        <v>15821</v>
+        <v>19823</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>92.90000000000001</v>
+        <v>147.53</v>
       </c>
       <c r="B416" t="n">
-        <v>28619</v>
+        <v>21164</v>
       </c>
       <c r="C416" t="n">
-        <v>94.84999999999999</v>
+        <v>128.26</v>
       </c>
       <c r="D416" t="n">
-        <v>24053</v>
+        <v>27083</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>110.51</v>
+        <v>148.54</v>
       </c>
       <c r="B417" t="n">
-        <v>30191</v>
+        <v>25481</v>
       </c>
       <c r="C417" t="n">
-        <v>107.23</v>
+        <v>147.51</v>
       </c>
       <c r="D417" t="n">
-        <v>16304</v>
+        <v>24515</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>11.19</v>
+        <v>148.62</v>
       </c>
       <c r="B418" t="n">
-        <v>24109</v>
+        <v>22642</v>
       </c>
       <c r="C418" t="n">
-        <v>11.16</v>
+        <v>180</v>
       </c>
       <c r="D418" t="n">
-        <v>11390</v>
+        <v>29429</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>108.29</v>
+        <v>149.18</v>
       </c>
       <c r="B419" t="n">
-        <v>37780</v>
+        <v>21235</v>
       </c>
       <c r="C419" t="n">
-        <v>107.08</v>
+        <v>125.69</v>
       </c>
       <c r="D419" t="n">
-        <v>27911</v>
+        <v>28121</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>95.64</v>
+        <v>150.08</v>
       </c>
       <c r="B420" t="n">
-        <v>37562</v>
+        <v>23653</v>
       </c>
       <c r="C420" t="n">
-        <v>96.38</v>
+        <v>156.72</v>
       </c>
       <c r="D420" t="n">
-        <v>25801</v>
+        <v>26268</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>95.94</v>
+        <v>150.15</v>
       </c>
       <c r="B421" t="n">
-        <v>36089</v>
+        <v>24919</v>
       </c>
       <c r="C421" t="n">
-        <v>93.59999999999999</v>
+        <v>133.53</v>
       </c>
       <c r="D421" t="n">
-        <v>14628</v>
+        <v>20436</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>114.06</v>
+        <v>150.42</v>
       </c>
       <c r="B422" t="n">
-        <v>22397</v>
+        <v>22541</v>
       </c>
       <c r="C422" t="n">
-        <v>113.75</v>
+        <v>123.82</v>
       </c>
       <c r="D422" t="n">
-        <v>13894</v>
+        <v>10229</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>93.89</v>
+        <v>150.53</v>
       </c>
       <c r="B423" t="n">
-        <v>29162</v>
+        <v>21225</v>
       </c>
       <c r="C423" t="n">
-        <v>95.19</v>
+        <v>178.79</v>
       </c>
       <c r="D423" t="n">
-        <v>10886</v>
+        <v>10611</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>106.63</v>
+        <v>150.57</v>
       </c>
       <c r="B424" t="n">
-        <v>42929</v>
+        <v>22174</v>
       </c>
       <c r="C424" t="n">
-        <v>106.72</v>
+        <v>180</v>
       </c>
       <c r="D424" t="n">
-        <v>14617</v>
+        <v>25081</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>113.56</v>
+        <v>150.69</v>
       </c>
       <c r="B425" t="n">
-        <v>24786</v>
+        <v>22007</v>
       </c>
       <c r="C425" t="n">
-        <v>116.75</v>
+        <v>120.91</v>
       </c>
       <c r="D425" t="n">
-        <v>13754</v>
+        <v>16486</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>90.18000000000001</v>
+        <v>150.74</v>
       </c>
       <c r="B426" t="n">
-        <v>23337</v>
+        <v>21136</v>
       </c>
       <c r="C426" t="n">
-        <v>92.59</v>
+        <v>130.25</v>
       </c>
       <c r="D426" t="n">
-        <v>21197</v>
+        <v>13028</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>172.22</v>
+        <v>151.46</v>
       </c>
       <c r="B427" t="n">
-        <v>23147</v>
+        <v>24999</v>
       </c>
       <c r="C427" t="n">
-        <v>177.99</v>
+        <v>163.31</v>
       </c>
       <c r="D427" t="n">
-        <v>21089</v>
+        <v>15395</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>102.79</v>
+        <v>151.58</v>
       </c>
       <c r="B428" t="n">
-        <v>46731</v>
+        <v>26606</v>
       </c>
       <c r="C428" t="n">
-        <v>106.97</v>
+        <v>155.84</v>
       </c>
       <c r="D428" t="n">
-        <v>27118</v>
+        <v>20387</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>99.73999999999999</v>
+        <v>152.28</v>
       </c>
       <c r="B429" t="n">
-        <v>42831</v>
+        <v>28060</v>
       </c>
       <c r="C429" t="n">
-        <v>97.53</v>
+        <v>174.45</v>
       </c>
       <c r="D429" t="n">
-        <v>29420</v>
+        <v>15673</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>101.15</v>
+        <v>152.45</v>
       </c>
       <c r="B430" t="n">
-        <v>46877</v>
+        <v>24648</v>
       </c>
       <c r="C430" t="n">
-        <v>99.95</v>
+        <v>139.04</v>
       </c>
       <c r="D430" t="n">
-        <v>28718</v>
+        <v>26924</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>110.12</v>
+        <v>152.47</v>
       </c>
       <c r="B431" t="n">
-        <v>34838</v>
+        <v>28420</v>
       </c>
       <c r="C431" t="n">
-        <v>110.1</v>
+        <v>155.16</v>
       </c>
       <c r="D431" t="n">
-        <v>25785</v>
+        <v>15380</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>106.19</v>
+        <v>152.95</v>
       </c>
       <c r="B432" t="n">
-        <v>42754</v>
+        <v>24743</v>
       </c>
       <c r="C432" t="n">
-        <v>107.25</v>
+        <v>134.15</v>
       </c>
       <c r="D432" t="n">
-        <v>24001</v>
+        <v>13384</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>92.70999999999999</v>
+        <v>153.11</v>
       </c>
       <c r="B433" t="n">
-        <v>29624</v>
+        <v>27900</v>
       </c>
       <c r="C433" t="n">
-        <v>89.20999999999999</v>
+        <v>138.93</v>
       </c>
       <c r="D433" t="n">
-        <v>21859</v>
+        <v>22828</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>90.06</v>
+        <v>153.21</v>
       </c>
       <c r="B434" t="n">
-        <v>24781</v>
+        <v>28912</v>
       </c>
       <c r="C434" t="n">
-        <v>87.59</v>
+        <v>180</v>
       </c>
       <c r="D434" t="n">
-        <v>10889</v>
+        <v>29439</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>114.9</v>
+        <v>153.23</v>
       </c>
       <c r="B435" t="n">
-        <v>20048</v>
+        <v>24925</v>
       </c>
       <c r="C435" t="n">
-        <v>111.89</v>
+        <v>175.77</v>
       </c>
       <c r="D435" t="n">
-        <v>12234</v>
+        <v>23283</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>99</v>
+        <v>153.35</v>
       </c>
       <c r="B436" t="n">
-        <v>41188</v>
+        <v>25493</v>
       </c>
       <c r="C436" t="n">
-        <v>96.05</v>
+        <v>163.81</v>
       </c>
       <c r="D436" t="n">
-        <v>27879</v>
+        <v>17407</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>119.64</v>
+        <v>153.75</v>
       </c>
       <c r="B437" t="n">
-        <v>24047</v>
+        <v>26890</v>
       </c>
       <c r="C437" t="n">
-        <v>117.55</v>
+        <v>125.65</v>
       </c>
       <c r="D437" t="n">
-        <v>16188</v>
+        <v>17755</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>124.9</v>
+        <v>154.69</v>
       </c>
       <c r="B438" t="n">
-        <v>22154</v>
+        <v>27804</v>
       </c>
       <c r="C438" t="n">
-        <v>126.16</v>
+        <v>159.24</v>
       </c>
       <c r="D438" t="n">
-        <v>17778</v>
+        <v>25768</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>96.56</v>
+        <v>155.04</v>
       </c>
       <c r="B439" t="n">
-        <v>35790</v>
+        <v>27714</v>
       </c>
       <c r="C439" t="n">
-        <v>93.45999999999999</v>
+        <v>177.29</v>
       </c>
       <c r="D439" t="n">
-        <v>10562</v>
+        <v>24699</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>104.22</v>
+        <v>155.45</v>
       </c>
       <c r="B440" t="n">
-        <v>45058</v>
+        <v>28374</v>
       </c>
       <c r="C440" t="n">
-        <v>102.65</v>
+        <v>125.15</v>
       </c>
       <c r="D440" t="n">
-        <v>28374</v>
+        <v>24161</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>113.54</v>
+        <v>155.68</v>
       </c>
       <c r="B441" t="n">
-        <v>24915</v>
+        <v>28228</v>
       </c>
       <c r="C441" t="n">
-        <v>111.25</v>
+        <v>165.02</v>
       </c>
       <c r="D441" t="n">
-        <v>19235</v>
+        <v>23736</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>18.16</v>
+        <v>156.1</v>
       </c>
       <c r="B442" t="n">
-        <v>23559</v>
+        <v>31071</v>
       </c>
       <c r="C442" t="n">
-        <v>18.44</v>
+        <v>180</v>
       </c>
       <c r="D442" t="n">
-        <v>23603</v>
+        <v>20422</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>96.58</v>
+        <v>156.2</v>
       </c>
       <c r="B443" t="n">
-        <v>38954</v>
+        <v>31012</v>
       </c>
       <c r="C443" t="n">
-        <v>96.56</v>
+        <v>180</v>
       </c>
       <c r="D443" t="n">
-        <v>11806</v>
+        <v>22144</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>94.90000000000001</v>
+        <v>156.49</v>
       </c>
       <c r="B444" t="n">
-        <v>33281</v>
+        <v>28413</v>
       </c>
       <c r="C444" t="n">
-        <v>92.78</v>
+        <v>149.87</v>
       </c>
       <c r="D444" t="n">
-        <v>10206</v>
+        <v>23028</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>99.59999999999999</v>
+        <v>157.39</v>
       </c>
       <c r="B445" t="n">
-        <v>43605</v>
+        <v>30370</v>
       </c>
       <c r="C445" t="n">
-        <v>97.94</v>
+        <v>162.42</v>
       </c>
       <c r="D445" t="n">
-        <v>26923</v>
+        <v>18515</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>116.97</v>
+        <v>157.62</v>
       </c>
       <c r="B446" t="n">
-        <v>25425</v>
+        <v>30642</v>
       </c>
       <c r="C446" t="n">
-        <v>118.22</v>
+        <v>176.88</v>
       </c>
       <c r="D446" t="n">
-        <v>23245</v>
+        <v>24635</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>111.09</v>
+        <v>157.97</v>
       </c>
       <c r="B447" t="n">
-        <v>28204</v>
+        <v>32014</v>
       </c>
       <c r="C447" t="n">
-        <v>111.18</v>
+        <v>148.86</v>
       </c>
       <c r="D447" t="n">
-        <v>25566</v>
+        <v>18051</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>76.84999999999999</v>
+        <v>157.98</v>
       </c>
       <c r="B448" t="n">
-        <v>22047</v>
+        <v>30048</v>
       </c>
       <c r="C448" t="n">
-        <v>79.56999999999999</v>
+        <v>168.65</v>
       </c>
       <c r="D448" t="n">
-        <v>14673</v>
+        <v>21542</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>92.68000000000001</v>
+        <v>158.06</v>
       </c>
       <c r="B449" t="n">
-        <v>26813</v>
+        <v>30594</v>
       </c>
       <c r="C449" t="n">
-        <v>92.59999999999999</v>
+        <v>176.63</v>
       </c>
       <c r="D449" t="n">
-        <v>27132</v>
+        <v>16449</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>107.67</v>
+        <v>158.53</v>
       </c>
       <c r="B450" t="n">
-        <v>41904</v>
+        <v>30225</v>
       </c>
       <c r="C450" t="n">
-        <v>107</v>
+        <v>143.63</v>
       </c>
       <c r="D450" t="n">
-        <v>14839</v>
+        <v>25324</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>103.73</v>
+        <v>158.87</v>
       </c>
       <c r="B451" t="n">
-        <v>49010</v>
+        <v>31606</v>
       </c>
       <c r="C451" t="n">
-        <v>100.36</v>
+        <v>179.63</v>
       </c>
       <c r="D451" t="n">
-        <v>18159</v>
+        <v>27570</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>100.28</v>
+        <v>159.07</v>
       </c>
       <c r="B452" t="n">
-        <v>45276</v>
+        <v>28499</v>
       </c>
       <c r="C452" t="n">
-        <v>97.36</v>
+        <v>136.5</v>
       </c>
       <c r="D452" t="n">
-        <v>14813</v>
+        <v>10054</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>74.33</v>
+        <v>159.12</v>
       </c>
       <c r="B453" t="n">
-        <v>22382</v>
+        <v>29517</v>
       </c>
       <c r="C453" t="n">
-        <v>73.28</v>
+        <v>155.52</v>
       </c>
       <c r="D453" t="n">
-        <v>11353</v>
+        <v>16221</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>176.38</v>
+        <v>159.13</v>
       </c>
       <c r="B454" t="n">
-        <v>25171</v>
+        <v>29310</v>
       </c>
       <c r="C454" t="n">
-        <v>178.1</v>
+        <v>180</v>
       </c>
       <c r="D454" t="n">
-        <v>22876</v>
+        <v>25020</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>90.79000000000001</v>
+        <v>159.7</v>
       </c>
       <c r="B455" t="n">
-        <v>22024</v>
+        <v>31651</v>
       </c>
       <c r="C455" t="n">
-        <v>90.25</v>
+        <v>159.87</v>
       </c>
       <c r="D455" t="n">
-        <v>16028</v>
+        <v>15652</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>109.07</v>
+        <v>160.42</v>
       </c>
       <c r="B456" t="n">
-        <v>34978</v>
+        <v>31833</v>
       </c>
       <c r="C456" t="n">
-        <v>107.84</v>
+        <v>148.54</v>
       </c>
       <c r="D456" t="n">
-        <v>28494</v>
+        <v>23808</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>100</v>
+        <v>160.46</v>
       </c>
       <c r="B457" t="n">
-        <v>44667</v>
+        <v>32230</v>
       </c>
       <c r="C457" t="n">
-        <v>101.22</v>
+        <v>179.81</v>
       </c>
       <c r="D457" t="n">
-        <v>10228</v>
+        <v>21396</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>108.02</v>
+        <v>161.13</v>
       </c>
       <c r="B458" t="n">
-        <v>39747</v>
+        <v>29613</v>
       </c>
       <c r="C458" t="n">
-        <v>106.89</v>
+        <v>176.5</v>
       </c>
       <c r="D458" t="n">
-        <v>20557</v>
+        <v>16198</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>94.87</v>
+        <v>161.15</v>
       </c>
       <c r="B459" t="n">
-        <v>31500</v>
+        <v>30695</v>
       </c>
       <c r="C459" t="n">
-        <v>92.17</v>
+        <v>166.65</v>
       </c>
       <c r="D459" t="n">
-        <v>24600</v>
+        <v>24089</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>114.5</v>
+        <v>161.53</v>
       </c>
       <c r="B460" t="n">
-        <v>23658</v>
+        <v>29639</v>
       </c>
       <c r="C460" t="n">
-        <v>113.24</v>
+        <v>148.28</v>
       </c>
       <c r="D460" t="n">
-        <v>27416</v>
+        <v>13267</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>100.2</v>
+        <v>162.53</v>
       </c>
       <c r="B461" t="n">
-        <v>43366</v>
+        <v>29786</v>
       </c>
       <c r="C461" t="n">
-        <v>98.27</v>
+        <v>177.41</v>
       </c>
       <c r="D461" t="n">
-        <v>28347</v>
+        <v>12346</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>99.51000000000001</v>
+        <v>162.96</v>
       </c>
       <c r="B462" t="n">
-        <v>43901</v>
+        <v>30975</v>
       </c>
       <c r="C462" t="n">
-        <v>96.14</v>
+        <v>180</v>
       </c>
       <c r="D462" t="n">
-        <v>26751</v>
+        <v>17925</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>103.72</v>
+        <v>162.98</v>
       </c>
       <c r="B463" t="n">
-        <v>47188</v>
+        <v>27847</v>
       </c>
       <c r="C463" t="n">
-        <v>107.31</v>
+        <v>146.4</v>
       </c>
       <c r="D463" t="n">
-        <v>21595</v>
+        <v>25839</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>42.11</v>
+        <v>163</v>
       </c>
       <c r="B464" t="n">
-        <v>23861</v>
+        <v>27180</v>
       </c>
       <c r="C464" t="n">
-        <v>41.3</v>
+        <v>167.36</v>
       </c>
       <c r="D464" t="n">
-        <v>14884</v>
+        <v>24283</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>73.97</v>
+        <v>164.26</v>
       </c>
       <c r="B465" t="n">
-        <v>24906</v>
+        <v>25211</v>
       </c>
       <c r="C465" t="n">
-        <v>75.11</v>
+        <v>155.16</v>
       </c>
       <c r="D465" t="n">
-        <v>15840</v>
+        <v>19144</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>105.16</v>
+        <v>164.73</v>
       </c>
       <c r="B466" t="n">
-        <v>46181</v>
+        <v>27325</v>
       </c>
       <c r="C466" t="n">
-        <v>103.96</v>
+        <v>175.26</v>
       </c>
       <c r="D466" t="n">
-        <v>13178</v>
+        <v>20724</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>19.24</v>
+        <v>166.21</v>
       </c>
       <c r="B467" t="n">
-        <v>25818</v>
+        <v>27041</v>
       </c>
       <c r="C467" t="n">
-        <v>19.13</v>
+        <v>153.95</v>
       </c>
       <c r="D467" t="n">
-        <v>10400</v>
+        <v>28743</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>93.11</v>
+        <v>166.48</v>
       </c>
       <c r="B468" t="n">
-        <v>29734</v>
+        <v>25527</v>
       </c>
       <c r="C468" t="n">
-        <v>91.92</v>
+        <v>140.52</v>
       </c>
       <c r="D468" t="n">
-        <v>18507</v>
+        <v>13816</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>92.7</v>
+        <v>166.9</v>
       </c>
       <c r="B469" t="n">
-        <v>28695</v>
+        <v>25743</v>
       </c>
       <c r="C469" t="n">
-        <v>89.17</v>
+        <v>156.13</v>
       </c>
       <c r="D469" t="n">
-        <v>18099</v>
+        <v>24804</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>112.43</v>
+        <v>167.12</v>
       </c>
       <c r="B470" t="n">
-        <v>26213</v>
+        <v>25799</v>
       </c>
       <c r="C470" t="n">
-        <v>111.55</v>
+        <v>180</v>
       </c>
       <c r="D470" t="n">
-        <v>28790</v>
+        <v>16318</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>103.41</v>
+        <v>167.87</v>
       </c>
       <c r="B471" t="n">
-        <v>48113</v>
+        <v>22628</v>
       </c>
       <c r="C471" t="n">
-        <v>105.94</v>
+        <v>163.2</v>
       </c>
       <c r="D471" t="n">
-        <v>20763</v>
+        <v>18352</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>111.51</v>
+        <v>168.5</v>
       </c>
       <c r="B472" t="n">
-        <v>28326</v>
+        <v>23660</v>
       </c>
       <c r="C472" t="n">
-        <v>107.49</v>
+        <v>146.07</v>
       </c>
       <c r="D472" t="n">
-        <v>10570</v>
+        <v>15927</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>96.08</v>
+        <v>168.58</v>
       </c>
       <c r="B473" t="n">
-        <v>37899</v>
+        <v>24043</v>
       </c>
       <c r="C473" t="n">
-        <v>95.73999999999999</v>
+        <v>142.3</v>
       </c>
       <c r="D473" t="n">
-        <v>16728</v>
+        <v>12275</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>94.89</v>
+        <v>168.59</v>
       </c>
       <c r="B474" t="n">
-        <v>36054</v>
+        <v>21709</v>
       </c>
       <c r="C474" t="n">
-        <v>93.78</v>
+        <v>150.77</v>
       </c>
       <c r="D474" t="n">
-        <v>28017</v>
+        <v>16897</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>99.26000000000001</v>
+        <v>169.15</v>
       </c>
       <c r="B475" t="n">
-        <v>43617</v>
+        <v>23842</v>
       </c>
       <c r="C475" t="n">
-        <v>97.39</v>
+        <v>144.19</v>
       </c>
       <c r="D475" t="n">
-        <v>27743</v>
+        <v>19821</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>102.64</v>
+        <v>169.17</v>
       </c>
       <c r="B476" t="n">
-        <v>47551</v>
+        <v>24055</v>
       </c>
       <c r="C476" t="n">
-        <v>100.2</v>
+        <v>154.02</v>
       </c>
       <c r="D476" t="n">
-        <v>11611</v>
+        <v>27176</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>92.59999999999999</v>
+        <v>169.28</v>
       </c>
       <c r="B477" t="n">
-        <v>26333</v>
+        <v>24525</v>
       </c>
       <c r="C477" t="n">
-        <v>91.94</v>
+        <v>180</v>
       </c>
       <c r="D477" t="n">
-        <v>11504</v>
+        <v>22986</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>109.23</v>
+        <v>170.57</v>
       </c>
       <c r="B478" t="n">
-        <v>33847</v>
+        <v>20212</v>
       </c>
       <c r="C478" t="n">
-        <v>109.41</v>
+        <v>167.48</v>
       </c>
       <c r="D478" t="n">
-        <v>18198</v>
+        <v>14950</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>93.90000000000001</v>
+        <v>171.18</v>
       </c>
       <c r="B479" t="n">
-        <v>30978</v>
+        <v>19714</v>
       </c>
       <c r="C479" t="n">
-        <v>95.73999999999999</v>
+        <v>172.08</v>
       </c>
       <c r="D479" t="n">
-        <v>28969</v>
+        <v>21848</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>110.15</v>
+        <v>172.01</v>
       </c>
       <c r="B480" t="n">
-        <v>31569</v>
+        <v>20582</v>
       </c>
       <c r="C480" t="n">
-        <v>105.58</v>
+        <v>165.83</v>
       </c>
       <c r="D480" t="n">
-        <v>15869</v>
+        <v>25985</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>101.94</v>
+        <v>172.4</v>
       </c>
       <c r="B481" t="n">
-        <v>45469</v>
+        <v>21149</v>
       </c>
       <c r="C481" t="n">
-        <v>106.32</v>
+        <v>166.22</v>
       </c>
       <c r="D481" t="n">
-        <v>28325</v>
+        <v>19239</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>108.96</v>
+        <v>172.43</v>
       </c>
       <c r="B482" t="n">
-        <v>37351</v>
+        <v>20439</v>
       </c>
       <c r="C482" t="n">
-        <v>109.08</v>
+        <v>174.29</v>
       </c>
       <c r="D482" t="n">
-        <v>12109</v>
+        <v>14877</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>94.89</v>
+        <v>172.59</v>
       </c>
       <c r="B483" t="n">
-        <v>35151</v>
+        <v>22031</v>
       </c>
       <c r="C483" t="n">
-        <v>97.69</v>
+        <v>155.78</v>
       </c>
       <c r="D483" t="n">
-        <v>24124</v>
+        <v>29355</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>176.17</v>
+        <v>173.1</v>
       </c>
       <c r="B484" t="n">
-        <v>23977</v>
+        <v>21817</v>
       </c>
       <c r="C484" t="n">
-        <v>170.16</v>
+        <v>180</v>
       </c>
       <c r="D484" t="n">
-        <v>20945</v>
+        <v>18150</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>146.32</v>
+        <v>173.12</v>
       </c>
       <c r="B485" t="n">
-        <v>23067</v>
+        <v>21941</v>
       </c>
       <c r="C485" t="n">
-        <v>142.65</v>
+        <v>180</v>
       </c>
       <c r="D485" t="n">
-        <v>29487</v>
+        <v>16718</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>98.83</v>
+        <v>173.78</v>
       </c>
       <c r="B486" t="n">
-        <v>39210</v>
+        <v>20996</v>
       </c>
       <c r="C486" t="n">
-        <v>96.78</v>
+        <v>180</v>
       </c>
       <c r="D486" t="n">
-        <v>13125</v>
+        <v>10095</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>27.9</v>
+        <v>174.37</v>
       </c>
       <c r="B487" t="n">
-        <v>21726</v>
+        <v>20340</v>
       </c>
       <c r="C487" t="n">
-        <v>28.46</v>
+        <v>180</v>
       </c>
       <c r="D487" t="n">
-        <v>13848</v>
+        <v>28611</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>62.85</v>
+        <v>174.62</v>
       </c>
       <c r="B488" t="n">
-        <v>23655</v>
+        <v>18354</v>
       </c>
       <c r="C488" t="n">
-        <v>62.11</v>
+        <v>180</v>
       </c>
       <c r="D488" t="n">
-        <v>23745</v>
+        <v>14413</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>104.06</v>
+        <v>174.64</v>
       </c>
       <c r="B489" t="n">
-        <v>48138</v>
+        <v>20105</v>
       </c>
       <c r="C489" t="n">
-        <v>103.37</v>
+        <v>154.89</v>
       </c>
       <c r="D489" t="n">
-        <v>29349</v>
+        <v>12934</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>85.20999999999999</v>
+        <v>175.02</v>
       </c>
       <c r="B490" t="n">
-        <v>24381</v>
+        <v>19496</v>
       </c>
       <c r="C490" t="n">
-        <v>87.42</v>
+        <v>180</v>
       </c>
       <c r="D490" t="n">
-        <v>16122</v>
+        <v>26554</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>109.94</v>
+        <v>175.26</v>
       </c>
       <c r="B491" t="n">
-        <v>32446</v>
+        <v>19691</v>
       </c>
       <c r="C491" t="n">
-        <v>112.96</v>
+        <v>171.78</v>
       </c>
       <c r="D491" t="n">
-        <v>21135</v>
+        <v>28660</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>130.29</v>
+        <v>175.29</v>
       </c>
       <c r="B492" t="n">
-        <v>23576</v>
+        <v>18407</v>
       </c>
       <c r="C492" t="n">
-        <v>131.01</v>
+        <v>167.54</v>
       </c>
       <c r="D492" t="n">
-        <v>22660</v>
+        <v>12275</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>106.49</v>
+        <v>175.42</v>
       </c>
       <c r="B493" t="n">
-        <v>45895</v>
+        <v>20128</v>
       </c>
       <c r="C493" t="n">
-        <v>108.26</v>
+        <v>153.91</v>
       </c>
       <c r="D493" t="n">
-        <v>17644</v>
+        <v>10664</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>132.84</v>
+        <v>176.1</v>
       </c>
       <c r="B494" t="n">
-        <v>23938</v>
+        <v>20780</v>
       </c>
       <c r="C494" t="n">
-        <v>133.23</v>
+        <v>180</v>
       </c>
       <c r="D494" t="n">
-        <v>20133</v>
+        <v>11495</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>107.91</v>
+        <v>176.32</v>
       </c>
       <c r="B495" t="n">
-        <v>38096</v>
+        <v>18436</v>
       </c>
       <c r="C495" t="n">
-        <v>108.54</v>
+        <v>180</v>
       </c>
       <c r="D495" t="n">
-        <v>24367</v>
+        <v>18970</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>107.71</v>
+        <v>176.55</v>
       </c>
       <c r="B496" t="n">
-        <v>40445</v>
+        <v>19023</v>
       </c>
       <c r="C496" t="n">
-        <v>106.94</v>
+        <v>173.81</v>
       </c>
       <c r="D496" t="n">
-        <v>24421</v>
+        <v>27031</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>107.99</v>
+        <v>176.79</v>
       </c>
       <c r="B497" t="n">
-        <v>39612</v>
+        <v>19368</v>
       </c>
       <c r="C497" t="n">
-        <v>112.18</v>
+        <v>180</v>
       </c>
       <c r="D497" t="n">
-        <v>11752</v>
+        <v>11159</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>112.09</v>
+        <v>177.14</v>
       </c>
       <c r="B498" t="n">
-        <v>26451</v>
+        <v>19572</v>
       </c>
       <c r="C498" t="n">
-        <v>107.68</v>
+        <v>143.86</v>
       </c>
       <c r="D498" t="n">
-        <v>25505</v>
+        <v>21078</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>108.86</v>
+        <v>177.49</v>
       </c>
       <c r="B499" t="n">
-        <v>35441</v>
+        <v>18544</v>
       </c>
       <c r="C499" t="n">
-        <v>106.31</v>
+        <v>139.33</v>
       </c>
       <c r="D499" t="n">
-        <v>21101</v>
+        <v>26278</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>109.66</v>
+        <v>178.84</v>
       </c>
       <c r="B500" t="n">
-        <v>32996</v>
+        <v>20947</v>
       </c>
       <c r="C500" t="n">
-        <v>106.14</v>
+        <v>167.28</v>
       </c>
       <c r="D500" t="n">
-        <v>17448</v>
+        <v>29338</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>93.2</v>
+        <v>178.85</v>
       </c>
       <c r="B501" t="n">
-        <v>28717</v>
+        <v>17142</v>
       </c>
       <c r="C501" t="n">
-        <v>91.83</v>
+        <v>180</v>
       </c>
       <c r="D501" t="n">
-        <v>13959</v>
+        <v>13766</v>
       </c>
     </row>
   </sheetData>
